--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_grids\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAA4A02-F856-4FDA-B9A7-41BF6CDC8F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E67D5B1-F520-4CF6-8C13-66DD34CB87E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -143,9 +143,6 @@
     <t>electricity used in transport</t>
   </si>
   <si>
-    <t>DEM</t>
-  </si>
-  <si>
     <t>daynite</t>
   </si>
   <si>
@@ -1869,6 +1866,9 @@
   </si>
   <si>
     <t>RESELC</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
 </sst>
 </file>
@@ -4259,35 +4259,35 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
         <v>37</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -4357,7 +4357,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -4389,19 +4389,19 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
+        <v>214</v>
+      </c>
+      <c r="O5" t="s">
         <v>215</v>
       </c>
-      <c r="O5" t="s">
-        <v>216</v>
-      </c>
       <c r="P5" t="s">
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -4409,7 +4409,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
@@ -4418,19 +4418,19 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
+        <v>217</v>
+      </c>
+      <c r="O6" t="s">
         <v>218</v>
       </c>
-      <c r="O6" t="s">
-        <v>219</v>
-      </c>
       <c r="P6" t="s">
         <v>25</v>
       </c>
       <c r="Q6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -4438,7 +4438,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -4447,19 +4447,19 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
+        <v>219</v>
+      </c>
+      <c r="O7" t="s">
         <v>220</v>
       </c>
-      <c r="O7" t="s">
-        <v>221</v>
-      </c>
       <c r="P7" t="s">
         <v>25</v>
       </c>
       <c r="Q7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -4476,19 +4476,19 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O8" t="s">
         <v>222</v>
       </c>
-      <c r="O8" t="s">
-        <v>223</v>
-      </c>
       <c r="P8" t="s">
         <v>25</v>
       </c>
       <c r="Q8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -4505,19 +4505,19 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O9" t="s">
         <v>224</v>
       </c>
-      <c r="O9" t="s">
-        <v>225</v>
-      </c>
       <c r="P9" t="s">
         <v>25</v>
       </c>
       <c r="Q9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -4534,19 +4534,19 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" t="s">
         <v>226</v>
       </c>
-      <c r="O10" t="s">
-        <v>227</v>
-      </c>
       <c r="P10" t="s">
         <v>25</v>
       </c>
       <c r="Q10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -4563,19 +4563,19 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
+        <v>227</v>
+      </c>
+      <c r="O11" t="s">
         <v>228</v>
       </c>
-      <c r="O11" t="s">
-        <v>229</v>
-      </c>
       <c r="P11" t="s">
         <v>25</v>
       </c>
       <c r="Q11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -4583,7 +4583,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -4592,19 +4592,19 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
+        <v>229</v>
+      </c>
+      <c r="O12" t="s">
         <v>230</v>
       </c>
-      <c r="O12" t="s">
-        <v>231</v>
-      </c>
       <c r="P12" t="s">
         <v>25</v>
       </c>
       <c r="Q12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -4621,19 +4621,19 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" t="s">
         <v>232</v>
       </c>
-      <c r="O13" t="s">
-        <v>233</v>
-      </c>
       <c r="P13" t="s">
         <v>25</v>
       </c>
       <c r="Q13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -4641,10 +4641,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -4653,19 +4653,19 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
+        <v>233</v>
+      </c>
+      <c r="O14" t="s">
         <v>234</v>
       </c>
-      <c r="O14" t="s">
-        <v>235</v>
-      </c>
       <c r="P14" t="s">
         <v>25</v>
       </c>
       <c r="Q14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -4673,10 +4673,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -4685,19 +4685,19 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
+        <v>235</v>
+      </c>
+      <c r="O15" t="s">
         <v>236</v>
       </c>
-      <c r="O15" t="s">
-        <v>237</v>
-      </c>
       <c r="P15" t="s">
         <v>25</v>
       </c>
       <c r="Q15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -4714,7 +4714,7 @@
         <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
@@ -4726,30 +4726,30 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
+        <v>237</v>
+      </c>
+      <c r="O16" t="s">
         <v>238</v>
       </c>
-      <c r="O16" t="s">
-        <v>239</v>
-      </c>
       <c r="P16" t="s">
         <v>25</v>
       </c>
       <c r="Q16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="2:18">
       <c r="B17" t="s">
-        <v>34</v>
+        <v>609</v>
       </c>
       <c r="C17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" t="s">
         <v>203</v>
-      </c>
-      <c r="D17" t="s">
-        <v>204</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
@@ -4758,24 +4758,24 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
+        <v>239</v>
+      </c>
+      <c r="O17" t="s">
         <v>240</v>
       </c>
-      <c r="O17" t="s">
-        <v>241</v>
-      </c>
       <c r="P17" t="s">
         <v>25</v>
       </c>
       <c r="Q17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="2:18">
       <c r="B18" t="s">
-        <v>34</v>
+        <v>609</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -4790,24 +4790,24 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
+        <v>241</v>
+      </c>
+      <c r="O18" t="s">
         <v>242</v>
       </c>
-      <c r="O18" t="s">
-        <v>243</v>
-      </c>
       <c r="P18" t="s">
         <v>25</v>
       </c>
       <c r="Q18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="2:18">
       <c r="B19" t="s">
-        <v>34</v>
+        <v>609</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
@@ -4822,24 +4822,24 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
+        <v>243</v>
+      </c>
+      <c r="O19" t="s">
         <v>244</v>
       </c>
-      <c r="O19" t="s">
-        <v>245</v>
-      </c>
       <c r="P19" t="s">
         <v>25</v>
       </c>
       <c r="Q19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="2:18">
       <c r="B20" t="s">
-        <v>34</v>
+        <v>609</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
@@ -4854,36 +4854,36 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
+        <v>245</v>
+      </c>
+      <c r="O20" t="s">
         <v>246</v>
       </c>
-      <c r="O20" t="s">
-        <v>247</v>
-      </c>
       <c r="P20" t="s">
         <v>25</v>
       </c>
       <c r="Q20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="2:18">
       <c r="B21" t="s">
-        <v>17</v>
+        <v>609</v>
       </c>
       <c r="C21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" t="s">
         <v>197</v>
-      </c>
-      <c r="D21" t="s">
-        <v>198</v>
       </c>
       <c r="E21" t="s">
         <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
         <v>25</v>
@@ -4892,109 +4892,109 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
+        <v>247</v>
+      </c>
+      <c r="O21" t="s">
         <v>248</v>
       </c>
-      <c r="O21" t="s">
-        <v>249</v>
-      </c>
       <c r="P21" t="s">
         <v>25</v>
       </c>
       <c r="Q21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="2:18">
       <c r="B22" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" t="s">
         <v>193</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>194</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>195</v>
       </c>
-      <c r="E22" t="s">
-        <v>196</v>
-      </c>
       <c r="M22" t="s">
         <v>17</v>
       </c>
       <c r="N22" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" t="s">
         <v>250</v>
       </c>
-      <c r="O22" t="s">
-        <v>251</v>
-      </c>
       <c r="P22" t="s">
         <v>25</v>
       </c>
       <c r="Q22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="2:18">
       <c r="B23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M23" t="s">
         <v>17</v>
       </c>
       <c r="N23" t="s">
+        <v>251</v>
+      </c>
+      <c r="O23" t="s">
         <v>252</v>
       </c>
-      <c r="O23" t="s">
-        <v>253</v>
-      </c>
       <c r="P23" t="s">
         <v>25</v>
       </c>
       <c r="Q23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="2:18">
       <c r="B24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M24" t="s">
         <v>17</v>
       </c>
       <c r="N24" t="s">
+        <v>253</v>
+      </c>
+      <c r="O24" t="s">
         <v>254</v>
       </c>
-      <c r="O24" t="s">
-        <v>255</v>
-      </c>
       <c r="P24" t="s">
         <v>25</v>
       </c>
       <c r="Q24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -5002,19 +5002,19 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
+        <v>255</v>
+      </c>
+      <c r="O25" t="s">
         <v>256</v>
       </c>
-      <c r="O25" t="s">
-        <v>257</v>
-      </c>
       <c r="P25" t="s">
         <v>25</v>
       </c>
       <c r="Q25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -5022,19 +5022,19 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
+        <v>257</v>
+      </c>
+      <c r="O26" t="s">
         <v>258</v>
       </c>
-      <c r="O26" t="s">
-        <v>259</v>
-      </c>
       <c r="P26" t="s">
         <v>25</v>
       </c>
       <c r="Q26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="2:18" ht="17.649999999999999" thickBot="1">
@@ -5047,19 +5047,19 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
+        <v>259</v>
+      </c>
+      <c r="O27" t="s">
         <v>260</v>
       </c>
-      <c r="O27" t="s">
-        <v>261</v>
-      </c>
       <c r="P27" t="s">
         <v>25</v>
       </c>
       <c r="Q27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="2:18" ht="15" thickTop="1" thickBot="1">
@@ -5073,34 +5073,34 @@
         <v>11</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>603</v>
-      </c>
       <c r="M28" t="s">
         <v>17</v>
       </c>
       <c r="N28" t="s">
+        <v>261</v>
+      </c>
+      <c r="O28" t="s">
         <v>262</v>
       </c>
-      <c r="O28" t="s">
-        <v>263</v>
-      </c>
       <c r="P28" t="s">
         <v>25</v>
       </c>
       <c r="Q28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="2:18">
@@ -5108,69 +5108,69 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
+        <v>603</v>
+      </c>
+      <c r="E29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" t="s">
         <v>604</v>
       </c>
-      <c r="E29" t="s">
-        <v>85</v>
-      </c>
-      <c r="F29" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" t="s">
-        <v>605</v>
-      </c>
       <c r="M29" t="s">
         <v>17</v>
       </c>
       <c r="N29" t="s">
+        <v>263</v>
+      </c>
+      <c r="O29" t="s">
         <v>264</v>
       </c>
-      <c r="O29" t="s">
-        <v>265</v>
-      </c>
       <c r="P29" t="s">
         <v>25</v>
       </c>
       <c r="Q29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="2:18">
       <c r="B30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H30" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="M30" t="s">
         <v>17</v>
       </c>
       <c r="N30" t="s">
+        <v>265</v>
+      </c>
+      <c r="O30" t="s">
         <v>266</v>
       </c>
-      <c r="O30" t="s">
-        <v>267</v>
-      </c>
       <c r="P30" t="s">
         <v>25</v>
       </c>
       <c r="Q30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -5178,34 +5178,34 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="M31" t="s">
         <v>17</v>
       </c>
       <c r="N31" t="s">
+        <v>267</v>
+      </c>
+      <c r="O31" t="s">
         <v>268</v>
       </c>
-      <c r="O31" t="s">
-        <v>269</v>
-      </c>
       <c r="P31" t="s">
         <v>25</v>
       </c>
       <c r="Q31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -5213,34 +5213,34 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="M32" t="s">
         <v>17</v>
       </c>
       <c r="N32" t="s">
+        <v>269</v>
+      </c>
+      <c r="O32" t="s">
         <v>270</v>
       </c>
-      <c r="O32" t="s">
-        <v>271</v>
-      </c>
       <c r="P32" t="s">
         <v>25</v>
       </c>
       <c r="Q32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="2:18">
@@ -5248,34 +5248,34 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="M33" t="s">
         <v>17</v>
       </c>
       <c r="N33" t="s">
+        <v>271</v>
+      </c>
+      <c r="O33" t="s">
         <v>272</v>
       </c>
-      <c r="O33" t="s">
-        <v>273</v>
-      </c>
       <c r="P33" t="s">
         <v>25</v>
       </c>
       <c r="Q33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="2:18">
@@ -5283,19 +5283,19 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
+        <v>273</v>
+      </c>
+      <c r="O34" t="s">
         <v>274</v>
       </c>
-      <c r="O34" t="s">
-        <v>275</v>
-      </c>
       <c r="P34" t="s">
         <v>25</v>
       </c>
       <c r="Q34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="2:18">
@@ -5303,19 +5303,19 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
+        <v>275</v>
+      </c>
+      <c r="O35" t="s">
         <v>276</v>
       </c>
-      <c r="O35" t="s">
-        <v>277</v>
-      </c>
       <c r="P35" t="s">
         <v>25</v>
       </c>
       <c r="Q35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="2:18">
@@ -5323,19 +5323,19 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
+        <v>277</v>
+      </c>
+      <c r="O36" t="s">
         <v>278</v>
       </c>
-      <c r="O36" t="s">
-        <v>279</v>
-      </c>
       <c r="P36" t="s">
         <v>25</v>
       </c>
       <c r="Q36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="2:18">
@@ -5343,19 +5343,19 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
+        <v>279</v>
+      </c>
+      <c r="O37" t="s">
         <v>280</v>
       </c>
-      <c r="O37" t="s">
-        <v>281</v>
-      </c>
       <c r="P37" t="s">
         <v>25</v>
       </c>
       <c r="Q37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="2:18">
@@ -5363,19 +5363,19 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
+        <v>281</v>
+      </c>
+      <c r="O38" t="s">
         <v>282</v>
       </c>
-      <c r="O38" t="s">
-        <v>283</v>
-      </c>
       <c r="P38" t="s">
         <v>25</v>
       </c>
       <c r="Q38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="2:18">
@@ -5383,19 +5383,19 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
+        <v>283</v>
+      </c>
+      <c r="O39" t="s">
         <v>284</v>
       </c>
-      <c r="O39" t="s">
-        <v>285</v>
-      </c>
       <c r="P39" t="s">
         <v>25</v>
       </c>
       <c r="Q39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="2:18">
@@ -5403,19 +5403,19 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
+        <v>285</v>
+      </c>
+      <c r="O40" t="s">
         <v>286</v>
       </c>
-      <c r="O40" t="s">
-        <v>287</v>
-      </c>
       <c r="P40" t="s">
         <v>25</v>
       </c>
       <c r="Q40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="2:18">
@@ -5423,19 +5423,19 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
+        <v>287</v>
+      </c>
+      <c r="O41" t="s">
         <v>288</v>
       </c>
-      <c r="O41" t="s">
-        <v>289</v>
-      </c>
       <c r="P41" t="s">
         <v>25</v>
       </c>
       <c r="Q41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="2:18">
@@ -5443,19 +5443,19 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
+        <v>289</v>
+      </c>
+      <c r="O42" t="s">
         <v>290</v>
       </c>
-      <c r="O42" t="s">
-        <v>291</v>
-      </c>
       <c r="P42" t="s">
         <v>25</v>
       </c>
       <c r="Q42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="2:18">
@@ -5463,19 +5463,19 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
+        <v>291</v>
+      </c>
+      <c r="O43" t="s">
         <v>292</v>
       </c>
-      <c r="O43" t="s">
-        <v>293</v>
-      </c>
       <c r="P43" t="s">
         <v>25</v>
       </c>
       <c r="Q43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="2:18">
@@ -5483,19 +5483,19 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
+        <v>293</v>
+      </c>
+      <c r="O44" t="s">
         <v>294</v>
       </c>
-      <c r="O44" t="s">
-        <v>295</v>
-      </c>
       <c r="P44" t="s">
         <v>25</v>
       </c>
       <c r="Q44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="2:18">
@@ -5503,19 +5503,19 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
+        <v>295</v>
+      </c>
+      <c r="O45" t="s">
         <v>296</v>
       </c>
-      <c r="O45" t="s">
-        <v>297</v>
-      </c>
       <c r="P45" t="s">
         <v>25</v>
       </c>
       <c r="Q45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" spans="2:18">
@@ -5523,19 +5523,19 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
+        <v>297</v>
+      </c>
+      <c r="O46" t="s">
         <v>298</v>
       </c>
-      <c r="O46" t="s">
-        <v>299</v>
-      </c>
       <c r="P46" t="s">
         <v>25</v>
       </c>
       <c r="Q46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="2:18">
@@ -5543,19 +5543,19 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
+        <v>299</v>
+      </c>
+      <c r="O47" t="s">
         <v>300</v>
       </c>
-      <c r="O47" t="s">
-        <v>301</v>
-      </c>
       <c r="P47" t="s">
         <v>25</v>
       </c>
       <c r="Q47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" spans="2:18">
@@ -5563,19 +5563,19 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
+        <v>301</v>
+      </c>
+      <c r="O48" t="s">
         <v>302</v>
       </c>
-      <c r="O48" t="s">
-        <v>303</v>
-      </c>
       <c r="P48" t="s">
         <v>25</v>
       </c>
       <c r="Q48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -5583,19 +5583,19 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
+        <v>303</v>
+      </c>
+      <c r="O49" t="s">
         <v>304</v>
       </c>
-      <c r="O49" t="s">
-        <v>305</v>
-      </c>
       <c r="P49" t="s">
         <v>25</v>
       </c>
       <c r="Q49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -5603,19 +5603,19 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
+        <v>305</v>
+      </c>
+      <c r="O50" t="s">
         <v>306</v>
       </c>
-      <c r="O50" t="s">
-        <v>307</v>
-      </c>
       <c r="P50" t="s">
         <v>25</v>
       </c>
       <c r="Q50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -5623,19 +5623,19 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
+        <v>307</v>
+      </c>
+      <c r="O51" t="s">
         <v>308</v>
       </c>
-      <c r="O51" t="s">
-        <v>309</v>
-      </c>
       <c r="P51" t="s">
         <v>25</v>
       </c>
       <c r="Q51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -5643,19 +5643,19 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
+        <v>309</v>
+      </c>
+      <c r="O52" t="s">
         <v>310</v>
       </c>
-      <c r="O52" t="s">
-        <v>311</v>
-      </c>
       <c r="P52" t="s">
         <v>25</v>
       </c>
       <c r="Q52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -5663,19 +5663,19 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
+        <v>311</v>
+      </c>
+      <c r="O53" t="s">
         <v>312</v>
       </c>
-      <c r="O53" t="s">
-        <v>313</v>
-      </c>
       <c r="P53" t="s">
         <v>25</v>
       </c>
       <c r="Q53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -5683,19 +5683,19 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
+        <v>313</v>
+      </c>
+      <c r="O54" t="s">
         <v>314</v>
       </c>
-      <c r="O54" t="s">
-        <v>315</v>
-      </c>
       <c r="P54" t="s">
         <v>25</v>
       </c>
       <c r="Q54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
+        <v>315</v>
+      </c>
+      <c r="O55" t="s">
         <v>316</v>
       </c>
-      <c r="O55" t="s">
-        <v>317</v>
-      </c>
       <c r="P55" t="s">
         <v>25</v>
       </c>
       <c r="Q55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -5723,19 +5723,19 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
+        <v>317</v>
+      </c>
+      <c r="O56" t="s">
         <v>318</v>
       </c>
-      <c r="O56" t="s">
-        <v>319</v>
-      </c>
       <c r="P56" t="s">
         <v>25</v>
       </c>
       <c r="Q56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -5743,19 +5743,19 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
+        <v>319</v>
+      </c>
+      <c r="O57" t="s">
         <v>320</v>
       </c>
-      <c r="O57" t="s">
-        <v>321</v>
-      </c>
       <c r="P57" t="s">
         <v>25</v>
       </c>
       <c r="Q57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -5763,19 +5763,19 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
+        <v>321</v>
+      </c>
+      <c r="O58" t="s">
         <v>322</v>
       </c>
-      <c r="O58" t="s">
-        <v>323</v>
-      </c>
       <c r="P58" t="s">
         <v>25</v>
       </c>
       <c r="Q58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R58" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -5783,19 +5783,19 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
+        <v>323</v>
+      </c>
+      <c r="O59" t="s">
         <v>324</v>
       </c>
-      <c r="O59" t="s">
-        <v>325</v>
-      </c>
       <c r="P59" t="s">
         <v>25</v>
       </c>
       <c r="Q59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -5803,19 +5803,19 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
+        <v>325</v>
+      </c>
+      <c r="O60" t="s">
         <v>326</v>
       </c>
-      <c r="O60" t="s">
-        <v>327</v>
-      </c>
       <c r="P60" t="s">
         <v>25</v>
       </c>
       <c r="Q60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -5823,19 +5823,19 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
+        <v>327</v>
+      </c>
+      <c r="O61" t="s">
         <v>328</v>
       </c>
-      <c r="O61" t="s">
-        <v>329</v>
-      </c>
       <c r="P61" t="s">
         <v>25</v>
       </c>
       <c r="Q61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -5843,19 +5843,19 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
+        <v>329</v>
+      </c>
+      <c r="O62" t="s">
         <v>330</v>
       </c>
-      <c r="O62" t="s">
-        <v>331</v>
-      </c>
       <c r="P62" t="s">
         <v>25</v>
       </c>
       <c r="Q62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -5863,19 +5863,19 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
+        <v>331</v>
+      </c>
+      <c r="O63" t="s">
         <v>332</v>
       </c>
-      <c r="O63" t="s">
-        <v>333</v>
-      </c>
       <c r="P63" t="s">
         <v>25</v>
       </c>
       <c r="Q63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -5883,19 +5883,19 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
+        <v>333</v>
+      </c>
+      <c r="O64" t="s">
         <v>334</v>
       </c>
-      <c r="O64" t="s">
-        <v>335</v>
-      </c>
       <c r="P64" t="s">
         <v>25</v>
       </c>
       <c r="Q64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R64" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -5903,19 +5903,19 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
+        <v>335</v>
+      </c>
+      <c r="O65" t="s">
         <v>336</v>
       </c>
-      <c r="O65" t="s">
-        <v>337</v>
-      </c>
       <c r="P65" t="s">
         <v>25</v>
       </c>
       <c r="Q65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" spans="13:18">
@@ -5923,19 +5923,19 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
+        <v>337</v>
+      </c>
+      <c r="O66" t="s">
         <v>338</v>
       </c>
-      <c r="O66" t="s">
-        <v>339</v>
-      </c>
       <c r="P66" t="s">
         <v>25</v>
       </c>
       <c r="Q66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="13:18">
@@ -5943,19 +5943,19 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
+        <v>339</v>
+      </c>
+      <c r="O67" t="s">
         <v>340</v>
       </c>
-      <c r="O67" t="s">
-        <v>341</v>
-      </c>
       <c r="P67" t="s">
         <v>25</v>
       </c>
       <c r="Q67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="13:18">
@@ -5963,19 +5963,19 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
+        <v>341</v>
+      </c>
+      <c r="O68" t="s">
         <v>342</v>
       </c>
-      <c r="O68" t="s">
-        <v>343</v>
-      </c>
       <c r="P68" t="s">
         <v>25</v>
       </c>
       <c r="Q68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -6002,7 +6002,7 @@
   <sheetData>
     <row r="3" spans="2:7">
       <c r="B3" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -6012,28 +6012,28 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="14.25">
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="8" t="str">
         <f>"msy"&amp;COUNT(E14:E46)&amp;"_"&amp;MAX(E14:E46)</f>
@@ -6053,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="14.25">
@@ -6061,7 +6061,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" ref="E14:G14" si="1">$B$4</f>
@@ -6081,7 +6081,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" s="6">
         <f>E14+3</f>
@@ -6101,7 +6101,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E16" s="6">
         <f>E15+5</f>
@@ -6121,7 +6121,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" ref="E17:E20" si="2">E16+5</f>
@@ -6141,7 +6141,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" s="6">
         <f t="shared" si="2"/>
@@ -6161,7 +6161,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" s="6">
         <f t="shared" si="2"/>
@@ -6177,7 +6177,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" s="6">
         <f t="shared" si="2"/>
@@ -6189,7 +6189,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="14.25">
@@ -6197,7 +6197,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.25">
@@ -6205,7 +6205,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="14.25">
@@ -6213,37 +6213,37 @@
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="14.25">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="14.25">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="14.25">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="14.25">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="14.25">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="14.25">
@@ -6280,12 +6280,12 @@
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -6311,22 +6311,22 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" t="s">
         <v>345</v>
       </c>
-      <c r="D5" t="s">
-        <v>346</v>
-      </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -6334,22 +6334,22 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" t="s">
         <v>348</v>
       </c>
-      <c r="D6" t="s">
-        <v>349</v>
-      </c>
       <c r="E6" t="s">
         <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="2:8">
@@ -6357,22 +6357,22 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
+        <v>349</v>
+      </c>
+      <c r="D7" t="s">
         <v>350</v>
       </c>
-      <c r="D7" t="s">
-        <v>351</v>
-      </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:8">
@@ -6380,22 +6380,22 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
+        <v>351</v>
+      </c>
+      <c r="D8" t="s">
         <v>352</v>
       </c>
-      <c r="D8" t="s">
-        <v>353</v>
-      </c>
       <c r="E8" t="s">
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:8">
@@ -6403,22 +6403,22 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" t="s">
         <v>354</v>
       </c>
-      <c r="D9" t="s">
-        <v>355</v>
-      </c>
       <c r="E9" t="s">
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="2:8">
@@ -6426,22 +6426,22 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D10" t="s">
         <v>356</v>
       </c>
-      <c r="D10" t="s">
-        <v>357</v>
-      </c>
       <c r="E10" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -6449,22 +6449,22 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
+        <v>357</v>
+      </c>
+      <c r="D11" t="s">
         <v>358</v>
       </c>
-      <c r="D11" t="s">
-        <v>359</v>
-      </c>
       <c r="E11" t="s">
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="2:8">
@@ -6472,22 +6472,22 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D12" t="s">
         <v>360</v>
       </c>
-      <c r="D12" t="s">
-        <v>361</v>
-      </c>
       <c r="E12" t="s">
         <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -6495,22 +6495,22 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D13" t="s">
         <v>362</v>
       </c>
-      <c r="D13" t="s">
-        <v>363</v>
-      </c>
       <c r="E13" t="s">
         <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="2:8">
@@ -6518,22 +6518,22 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
+        <v>363</v>
+      </c>
+      <c r="D14" t="s">
         <v>364</v>
       </c>
-      <c r="D14" t="s">
-        <v>365</v>
-      </c>
       <c r="E14" t="s">
         <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="2:8">
@@ -6541,22 +6541,22 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
+        <v>365</v>
+      </c>
+      <c r="D15" t="s">
         <v>366</v>
       </c>
-      <c r="D15" t="s">
-        <v>367</v>
-      </c>
       <c r="E15" t="s">
         <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -6564,22 +6564,22 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
+        <v>367</v>
+      </c>
+      <c r="D16" t="s">
         <v>368</v>
       </c>
-      <c r="D16" t="s">
-        <v>369</v>
-      </c>
       <c r="E16" t="s">
         <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -6587,22 +6587,22 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
+        <v>369</v>
+      </c>
+      <c r="D17" t="s">
         <v>370</v>
       </c>
-      <c r="D17" t="s">
-        <v>371</v>
-      </c>
       <c r="E17" t="s">
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -6610,22 +6610,22 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
+        <v>371</v>
+      </c>
+      <c r="D18" t="s">
         <v>372</v>
       </c>
-      <c r="D18" t="s">
-        <v>373</v>
-      </c>
       <c r="E18" t="s">
         <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="2:8">
@@ -6633,22 +6633,22 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D19" t="s">
         <v>374</v>
       </c>
-      <c r="D19" t="s">
-        <v>375</v>
-      </c>
       <c r="E19" t="s">
         <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -6656,22 +6656,22 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
+        <v>375</v>
+      </c>
+      <c r="D20" t="s">
         <v>376</v>
       </c>
-      <c r="D20" t="s">
-        <v>377</v>
-      </c>
       <c r="E20" t="s">
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -6679,22 +6679,22 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
+        <v>377</v>
+      </c>
+      <c r="D21" t="s">
         <v>378</v>
       </c>
-      <c r="D21" t="s">
-        <v>379</v>
-      </c>
       <c r="E21" t="s">
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -6702,22 +6702,22 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
+        <v>379</v>
+      </c>
+      <c r="D22" t="s">
         <v>380</v>
       </c>
-      <c r="D22" t="s">
-        <v>381</v>
-      </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -6725,22 +6725,22 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
+        <v>381</v>
+      </c>
+      <c r="D23" t="s">
         <v>382</v>
       </c>
-      <c r="D23" t="s">
-        <v>383</v>
-      </c>
       <c r="E23" t="s">
         <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -6748,22 +6748,22 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
+        <v>383</v>
+      </c>
+      <c r="D24" t="s">
         <v>384</v>
       </c>
-      <c r="D24" t="s">
-        <v>385</v>
-      </c>
       <c r="E24" t="s">
         <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -6771,22 +6771,22 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
+        <v>385</v>
+      </c>
+      <c r="D25" t="s">
         <v>386</v>
       </c>
-      <c r="D25" t="s">
-        <v>387</v>
-      </c>
       <c r="E25" t="s">
         <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="2:8">
@@ -6794,22 +6794,22 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
+        <v>387</v>
+      </c>
+      <c r="D26" t="s">
         <v>388</v>
       </c>
-      <c r="D26" t="s">
-        <v>389</v>
-      </c>
       <c r="E26" t="s">
         <v>25</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -6817,22 +6817,22 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D27" t="s">
         <v>390</v>
       </c>
-      <c r="D27" t="s">
-        <v>391</v>
-      </c>
       <c r="E27" t="s">
         <v>25</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -6840,22 +6840,22 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
+        <v>391</v>
+      </c>
+      <c r="D28" t="s">
         <v>392</v>
       </c>
-      <c r="D28" t="s">
-        <v>393</v>
-      </c>
       <c r="E28" t="s">
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G28" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="2:8">
@@ -6863,22 +6863,22 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
+        <v>393</v>
+      </c>
+      <c r="D29" t="s">
         <v>394</v>
       </c>
-      <c r="D29" t="s">
-        <v>395</v>
-      </c>
       <c r="E29" t="s">
         <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="2:8">
@@ -6886,22 +6886,22 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
+        <v>395</v>
+      </c>
+      <c r="D30" t="s">
         <v>396</v>
       </c>
-      <c r="D30" t="s">
-        <v>397</v>
-      </c>
       <c r="E30" t="s">
         <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="2:8">
@@ -6909,22 +6909,22 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
+        <v>397</v>
+      </c>
+      <c r="D31" t="s">
         <v>398</v>
       </c>
-      <c r="D31" t="s">
-        <v>399</v>
-      </c>
       <c r="E31" t="s">
         <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G31" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="2:8">
@@ -6932,22 +6932,22 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
+        <v>399</v>
+      </c>
+      <c r="D32" t="s">
         <v>400</v>
       </c>
-      <c r="D32" t="s">
-        <v>401</v>
-      </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G32" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="2:8">
@@ -6955,22 +6955,22 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
+        <v>401</v>
+      </c>
+      <c r="D33" t="s">
         <v>402</v>
       </c>
-      <c r="D33" t="s">
-        <v>403</v>
-      </c>
       <c r="E33" t="s">
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="2:8">
@@ -6978,22 +6978,22 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
+        <v>403</v>
+      </c>
+      <c r="D34" t="s">
         <v>404</v>
       </c>
-      <c r="D34" t="s">
-        <v>405</v>
-      </c>
       <c r="E34" t="s">
         <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G34" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="2:8">
@@ -7001,22 +7001,22 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
+        <v>405</v>
+      </c>
+      <c r="D35" t="s">
         <v>406</v>
       </c>
-      <c r="D35" t="s">
-        <v>407</v>
-      </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G35" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="2:8">
@@ -7024,22 +7024,22 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
+        <v>407</v>
+      </c>
+      <c r="D36" t="s">
         <v>408</v>
       </c>
-      <c r="D36" t="s">
-        <v>409</v>
-      </c>
       <c r="E36" t="s">
         <v>25</v>
       </c>
       <c r="F36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G36" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="2:8">
@@ -7047,22 +7047,22 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
+        <v>409</v>
+      </c>
+      <c r="D37" t="s">
         <v>410</v>
       </c>
-      <c r="D37" t="s">
-        <v>411</v>
-      </c>
       <c r="E37" t="s">
         <v>25</v>
       </c>
       <c r="F37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G37" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="2:8">
@@ -7070,22 +7070,22 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
+        <v>411</v>
+      </c>
+      <c r="D38" t="s">
         <v>412</v>
       </c>
-      <c r="D38" t="s">
-        <v>413</v>
-      </c>
       <c r="E38" t="s">
         <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G38" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="2:8">
@@ -7093,22 +7093,22 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
+        <v>413</v>
+      </c>
+      <c r="D39" t="s">
         <v>414</v>
       </c>
-      <c r="D39" t="s">
-        <v>415</v>
-      </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G39" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="2:8">
@@ -7116,22 +7116,22 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
+        <v>415</v>
+      </c>
+      <c r="D40" t="s">
         <v>416</v>
       </c>
-      <c r="D40" t="s">
-        <v>417</v>
-      </c>
       <c r="E40" t="s">
         <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G40" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="2:8">
@@ -7139,22 +7139,22 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
+        <v>417</v>
+      </c>
+      <c r="D41" t="s">
         <v>418</v>
       </c>
-      <c r="D41" t="s">
-        <v>419</v>
-      </c>
       <c r="E41" t="s">
         <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G41" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="2:8">
@@ -7162,22 +7162,22 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
+        <v>419</v>
+      </c>
+      <c r="D42" t="s">
         <v>420</v>
       </c>
-      <c r="D42" t="s">
-        <v>421</v>
-      </c>
       <c r="E42" t="s">
         <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G42" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="2:8">
@@ -7185,22 +7185,22 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
+        <v>421</v>
+      </c>
+      <c r="D43" t="s">
         <v>422</v>
       </c>
-      <c r="D43" t="s">
-        <v>423</v>
-      </c>
       <c r="E43" t="s">
         <v>25</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="2:8">
@@ -7208,22 +7208,22 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
+        <v>423</v>
+      </c>
+      <c r="D44" t="s">
         <v>424</v>
       </c>
-      <c r="D44" t="s">
-        <v>425</v>
-      </c>
       <c r="E44" t="s">
         <v>25</v>
       </c>
       <c r="F44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G44" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="2:8">
@@ -7231,22 +7231,22 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
+        <v>425</v>
+      </c>
+      <c r="D45" t="s">
         <v>426</v>
       </c>
-      <c r="D45" t="s">
-        <v>427</v>
-      </c>
       <c r="E45" t="s">
         <v>25</v>
       </c>
       <c r="F45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G45" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" spans="2:8">
@@ -7254,22 +7254,22 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
+        <v>427</v>
+      </c>
+      <c r="D46" t="s">
         <v>428</v>
       </c>
-      <c r="D46" t="s">
-        <v>429</v>
-      </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G46" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="2:8">
@@ -7277,22 +7277,22 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
+        <v>429</v>
+      </c>
+      <c r="D47" t="s">
         <v>430</v>
       </c>
-      <c r="D47" t="s">
-        <v>431</v>
-      </c>
       <c r="E47" t="s">
         <v>25</v>
       </c>
       <c r="F47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G47" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" spans="2:8">
@@ -7300,22 +7300,22 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
+        <v>431</v>
+      </c>
+      <c r="D48" t="s">
         <v>432</v>
       </c>
-      <c r="D48" t="s">
-        <v>433</v>
-      </c>
       <c r="E48" t="s">
         <v>25</v>
       </c>
       <c r="F48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="2:8">
@@ -7323,22 +7323,22 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
+        <v>433</v>
+      </c>
+      <c r="D49" t="s">
         <v>434</v>
       </c>
-      <c r="D49" t="s">
-        <v>435</v>
-      </c>
       <c r="E49" t="s">
         <v>25</v>
       </c>
       <c r="F49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G49" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50" spans="2:8">
@@ -7346,22 +7346,22 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
+        <v>435</v>
+      </c>
+      <c r="D50" t="s">
         <v>436</v>
       </c>
-      <c r="D50" t="s">
-        <v>437</v>
-      </c>
       <c r="E50" t="s">
         <v>25</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G50" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="2:8">
@@ -7369,22 +7369,22 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
+        <v>437</v>
+      </c>
+      <c r="D51" t="s">
         <v>438</v>
       </c>
-      <c r="D51" t="s">
-        <v>439</v>
-      </c>
       <c r="E51" t="s">
         <v>25</v>
       </c>
       <c r="F51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52" spans="2:8">
@@ -7392,22 +7392,22 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
+        <v>439</v>
+      </c>
+      <c r="D52" t="s">
         <v>440</v>
       </c>
-      <c r="D52" t="s">
-        <v>441</v>
-      </c>
       <c r="E52" t="s">
         <v>25</v>
       </c>
       <c r="F52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G52" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" spans="2:8">
@@ -7415,22 +7415,22 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
+        <v>441</v>
+      </c>
+      <c r="D53" t="s">
         <v>442</v>
       </c>
-      <c r="D53" t="s">
-        <v>443</v>
-      </c>
       <c r="E53" t="s">
         <v>25</v>
       </c>
       <c r="F53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G53" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="2:8">
@@ -7438,22 +7438,22 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
+        <v>443</v>
+      </c>
+      <c r="D54" t="s">
         <v>444</v>
       </c>
-      <c r="D54" t="s">
-        <v>445</v>
-      </c>
       <c r="E54" t="s">
         <v>25</v>
       </c>
       <c r="F54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G54" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="2:8">
@@ -7461,22 +7461,22 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
+        <v>445</v>
+      </c>
+      <c r="D55" t="s">
         <v>446</v>
       </c>
-      <c r="D55" t="s">
-        <v>447</v>
-      </c>
       <c r="E55" t="s">
         <v>25</v>
       </c>
       <c r="F55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G55" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56" spans="2:8">
@@ -7484,22 +7484,22 @@
         <v>17</v>
       </c>
       <c r="C56" t="s">
+        <v>447</v>
+      </c>
+      <c r="D56" t="s">
         <v>448</v>
       </c>
-      <c r="D56" t="s">
-        <v>449</v>
-      </c>
       <c r="E56" t="s">
         <v>25</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G56" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="2:8">
@@ -7507,22 +7507,22 @@
         <v>17</v>
       </c>
       <c r="C57" t="s">
+        <v>449</v>
+      </c>
+      <c r="D57" t="s">
         <v>450</v>
       </c>
-      <c r="D57" t="s">
-        <v>451</v>
-      </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G57" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58" spans="2:8">
@@ -7530,22 +7530,22 @@
         <v>17</v>
       </c>
       <c r="C58" t="s">
+        <v>451</v>
+      </c>
+      <c r="D58" t="s">
         <v>452</v>
       </c>
-      <c r="D58" t="s">
-        <v>453</v>
-      </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G58" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H58" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="2:8">
@@ -7553,22 +7553,22 @@
         <v>17</v>
       </c>
       <c r="C59" t="s">
+        <v>453</v>
+      </c>
+      <c r="D59" t="s">
         <v>454</v>
       </c>
-      <c r="D59" t="s">
-        <v>455</v>
-      </c>
       <c r="E59" t="s">
         <v>25</v>
       </c>
       <c r="F59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G59" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" spans="2:8">
@@ -7576,22 +7576,22 @@
         <v>17</v>
       </c>
       <c r="C60" t="s">
+        <v>455</v>
+      </c>
+      <c r="D60" t="s">
         <v>456</v>
       </c>
-      <c r="D60" t="s">
-        <v>457</v>
-      </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G60" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="2:8">
@@ -7599,22 +7599,22 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
+        <v>457</v>
+      </c>
+      <c r="D61" t="s">
         <v>458</v>
       </c>
-      <c r="D61" t="s">
-        <v>459</v>
-      </c>
       <c r="E61" t="s">
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G61" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="2:8">
@@ -7622,22 +7622,22 @@
         <v>17</v>
       </c>
       <c r="C62" t="s">
+        <v>459</v>
+      </c>
+      <c r="D62" t="s">
         <v>460</v>
       </c>
-      <c r="D62" t="s">
-        <v>461</v>
-      </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G62" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -7645,22 +7645,22 @@
         <v>17</v>
       </c>
       <c r="C63" t="s">
+        <v>461</v>
+      </c>
+      <c r="D63" t="s">
         <v>462</v>
       </c>
-      <c r="D63" t="s">
-        <v>463</v>
-      </c>
       <c r="E63" t="s">
         <v>25</v>
       </c>
       <c r="F63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G63" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" spans="2:8">
@@ -7668,22 +7668,22 @@
         <v>17</v>
       </c>
       <c r="C64" t="s">
+        <v>463</v>
+      </c>
+      <c r="D64" t="s">
         <v>464</v>
       </c>
-      <c r="D64" t="s">
-        <v>465</v>
-      </c>
       <c r="E64" t="s">
         <v>25</v>
       </c>
       <c r="F64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G64" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H64" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" spans="2:8">
@@ -7691,22 +7691,22 @@
         <v>17</v>
       </c>
       <c r="C65" t="s">
+        <v>465</v>
+      </c>
+      <c r="D65" t="s">
         <v>466</v>
       </c>
-      <c r="D65" t="s">
-        <v>467</v>
-      </c>
       <c r="E65" t="s">
         <v>25</v>
       </c>
       <c r="F65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G65" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" spans="2:8">
@@ -7714,22 +7714,22 @@
         <v>17</v>
       </c>
       <c r="C66" t="s">
+        <v>467</v>
+      </c>
+      <c r="D66" t="s">
         <v>468</v>
       </c>
-      <c r="D66" t="s">
-        <v>469</v>
-      </c>
       <c r="E66" t="s">
         <v>25</v>
       </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G66" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="2:8">
@@ -7737,22 +7737,22 @@
         <v>17</v>
       </c>
       <c r="C67" t="s">
+        <v>469</v>
+      </c>
+      <c r="D67" t="s">
         <v>470</v>
       </c>
-      <c r="D67" t="s">
-        <v>471</v>
-      </c>
       <c r="E67" t="s">
         <v>25</v>
       </c>
       <c r="F67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G67" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="2:8">
@@ -7760,22 +7760,22 @@
         <v>17</v>
       </c>
       <c r="C68" t="s">
+        <v>471</v>
+      </c>
+      <c r="D68" t="s">
         <v>472</v>
       </c>
-      <c r="D68" t="s">
-        <v>473</v>
-      </c>
       <c r="E68" t="s">
         <v>25</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G68" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="69" spans="2:8">
@@ -7783,22 +7783,22 @@
         <v>17</v>
       </c>
       <c r="C69" t="s">
+        <v>473</v>
+      </c>
+      <c r="D69" t="s">
         <v>474</v>
       </c>
-      <c r="D69" t="s">
-        <v>475</v>
-      </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G69" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H69" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="70" spans="2:8">
@@ -7806,22 +7806,22 @@
         <v>17</v>
       </c>
       <c r="C70" t="s">
+        <v>475</v>
+      </c>
+      <c r="D70" t="s">
         <v>476</v>
       </c>
-      <c r="D70" t="s">
-        <v>477</v>
-      </c>
       <c r="E70" t="s">
         <v>25</v>
       </c>
       <c r="F70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G70" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H70" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="71" spans="2:8">
@@ -7829,22 +7829,22 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
+        <v>477</v>
+      </c>
+      <c r="D71" t="s">
         <v>478</v>
       </c>
-      <c r="D71" t="s">
-        <v>479</v>
-      </c>
       <c r="E71" t="s">
         <v>25</v>
       </c>
       <c r="F71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G71" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="2:8">
@@ -7852,22 +7852,22 @@
         <v>17</v>
       </c>
       <c r="C72" t="s">
+        <v>479</v>
+      </c>
+      <c r="D72" t="s">
         <v>480</v>
       </c>
-      <c r="D72" t="s">
-        <v>481</v>
-      </c>
       <c r="E72" t="s">
         <v>25</v>
       </c>
       <c r="F72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G72" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="73" spans="2:8">
@@ -7875,22 +7875,22 @@
         <v>17</v>
       </c>
       <c r="C73" t="s">
+        <v>481</v>
+      </c>
+      <c r="D73" t="s">
         <v>482</v>
       </c>
-      <c r="D73" t="s">
-        <v>483</v>
-      </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G73" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H73" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="74" spans="2:8">
@@ -7898,22 +7898,22 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
+        <v>483</v>
+      </c>
+      <c r="D74" t="s">
         <v>484</v>
       </c>
-      <c r="D74" t="s">
-        <v>485</v>
-      </c>
       <c r="E74" t="s">
         <v>25</v>
       </c>
       <c r="F74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G74" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" spans="2:8">
@@ -7921,22 +7921,22 @@
         <v>17</v>
       </c>
       <c r="C75" t="s">
+        <v>485</v>
+      </c>
+      <c r="D75" t="s">
         <v>486</v>
       </c>
-      <c r="D75" t="s">
-        <v>487</v>
-      </c>
       <c r="E75" t="s">
         <v>25</v>
       </c>
       <c r="F75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G75" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H75" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76" spans="2:8">
@@ -7944,22 +7944,22 @@
         <v>17</v>
       </c>
       <c r="C76" t="s">
+        <v>487</v>
+      </c>
+      <c r="D76" t="s">
         <v>488</v>
       </c>
-      <c r="D76" t="s">
-        <v>489</v>
-      </c>
       <c r="E76" t="s">
         <v>25</v>
       </c>
       <c r="F76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G76" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H76" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="77" spans="2:8">
@@ -7967,22 +7967,22 @@
         <v>17</v>
       </c>
       <c r="C77" t="s">
+        <v>489</v>
+      </c>
+      <c r="D77" t="s">
         <v>490</v>
       </c>
-      <c r="D77" t="s">
-        <v>491</v>
-      </c>
       <c r="E77" t="s">
         <v>25</v>
       </c>
       <c r="F77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G77" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="78" spans="2:8">
@@ -7990,22 +7990,22 @@
         <v>17</v>
       </c>
       <c r="C78" t="s">
+        <v>491</v>
+      </c>
+      <c r="D78" t="s">
         <v>492</v>
       </c>
-      <c r="D78" t="s">
-        <v>493</v>
-      </c>
       <c r="E78" t="s">
         <v>25</v>
       </c>
       <c r="F78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G78" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H78" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="79" spans="2:8">
@@ -8013,22 +8013,22 @@
         <v>17</v>
       </c>
       <c r="C79" t="s">
+        <v>493</v>
+      </c>
+      <c r="D79" t="s">
         <v>494</v>
       </c>
-      <c r="D79" t="s">
-        <v>495</v>
-      </c>
       <c r="E79" t="s">
         <v>25</v>
       </c>
       <c r="F79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G79" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H79" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -8036,22 +8036,22 @@
         <v>17</v>
       </c>
       <c r="C80" t="s">
+        <v>495</v>
+      </c>
+      <c r="D80" t="s">
         <v>496</v>
       </c>
-      <c r="D80" t="s">
-        <v>497</v>
-      </c>
       <c r="E80" t="s">
         <v>25</v>
       </c>
       <c r="F80" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G80" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H80" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -8059,22 +8059,22 @@
         <v>17</v>
       </c>
       <c r="C81" t="s">
+        <v>497</v>
+      </c>
+      <c r="D81" t="s">
         <v>498</v>
       </c>
-      <c r="D81" t="s">
-        <v>499</v>
-      </c>
       <c r="E81" t="s">
         <v>25</v>
       </c>
       <c r="F81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G81" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H81" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82" spans="2:8">
@@ -8082,22 +8082,22 @@
         <v>17</v>
       </c>
       <c r="C82" t="s">
+        <v>499</v>
+      </c>
+      <c r="D82" t="s">
         <v>500</v>
       </c>
-      <c r="D82" t="s">
-        <v>501</v>
-      </c>
       <c r="E82" t="s">
         <v>25</v>
       </c>
       <c r="F82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G82" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -8105,22 +8105,22 @@
         <v>17</v>
       </c>
       <c r="C83" t="s">
+        <v>501</v>
+      </c>
+      <c r="D83" t="s">
         <v>502</v>
       </c>
-      <c r="D83" t="s">
-        <v>503</v>
-      </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G83" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H83" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -8128,22 +8128,22 @@
         <v>17</v>
       </c>
       <c r="C84" t="s">
+        <v>503</v>
+      </c>
+      <c r="D84" t="s">
         <v>504</v>
       </c>
-      <c r="D84" t="s">
-        <v>505</v>
-      </c>
       <c r="E84" t="s">
         <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G84" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="85" spans="2:8">
@@ -8151,22 +8151,22 @@
         <v>17</v>
       </c>
       <c r="C85" t="s">
+        <v>505</v>
+      </c>
+      <c r="D85" t="s">
         <v>506</v>
       </c>
-      <c r="D85" t="s">
-        <v>507</v>
-      </c>
       <c r="E85" t="s">
         <v>25</v>
       </c>
       <c r="F85" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G85" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H85" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86" spans="2:8">
@@ -8174,22 +8174,22 @@
         <v>17</v>
       </c>
       <c r="C86" t="s">
+        <v>507</v>
+      </c>
+      <c r="D86" t="s">
         <v>508</v>
       </c>
-      <c r="D86" t="s">
-        <v>509</v>
-      </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G86" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="2:8">
@@ -8197,22 +8197,22 @@
         <v>17</v>
       </c>
       <c r="C87" t="s">
+        <v>509</v>
+      </c>
+      <c r="D87" t="s">
         <v>510</v>
       </c>
-      <c r="D87" t="s">
-        <v>511</v>
-      </c>
       <c r="E87" t="s">
         <v>25</v>
       </c>
       <c r="F87" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G87" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H87" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -8220,22 +8220,22 @@
         <v>17</v>
       </c>
       <c r="C88" t="s">
+        <v>511</v>
+      </c>
+      <c r="D88" t="s">
         <v>512</v>
       </c>
-      <c r="D88" t="s">
-        <v>513</v>
-      </c>
       <c r="E88" t="s">
         <v>25</v>
       </c>
       <c r="F88" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G88" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="2:8">
@@ -8243,22 +8243,22 @@
         <v>17</v>
       </c>
       <c r="C89" t="s">
+        <v>513</v>
+      </c>
+      <c r="D89" t="s">
         <v>514</v>
       </c>
-      <c r="D89" t="s">
-        <v>515</v>
-      </c>
       <c r="E89" t="s">
         <v>25</v>
       </c>
       <c r="F89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G89" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H89" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90" spans="2:8">
@@ -8266,22 +8266,22 @@
         <v>17</v>
       </c>
       <c r="C90" t="s">
+        <v>515</v>
+      </c>
+      <c r="D90" t="s">
         <v>516</v>
       </c>
-      <c r="D90" t="s">
-        <v>517</v>
-      </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G90" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H90" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -8289,22 +8289,22 @@
         <v>17</v>
       </c>
       <c r="C91" t="s">
+        <v>517</v>
+      </c>
+      <c r="D91" t="s">
         <v>518</v>
       </c>
-      <c r="D91" t="s">
-        <v>519</v>
-      </c>
       <c r="E91" t="s">
         <v>25</v>
       </c>
       <c r="F91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G91" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="92" spans="2:8">
@@ -8312,22 +8312,22 @@
         <v>17</v>
       </c>
       <c r="C92" t="s">
+        <v>519</v>
+      </c>
+      <c r="D92" t="s">
         <v>520</v>
       </c>
-      <c r="D92" t="s">
-        <v>521</v>
-      </c>
       <c r="E92" t="s">
         <v>25</v>
       </c>
       <c r="F92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G92" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H92" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="93" spans="2:8">
@@ -8335,22 +8335,22 @@
         <v>17</v>
       </c>
       <c r="C93" t="s">
+        <v>521</v>
+      </c>
+      <c r="D93" t="s">
         <v>522</v>
       </c>
-      <c r="D93" t="s">
-        <v>523</v>
-      </c>
       <c r="E93" t="s">
         <v>25</v>
       </c>
       <c r="F93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G93" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H93" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -8358,22 +8358,22 @@
         <v>17</v>
       </c>
       <c r="C94" t="s">
+        <v>523</v>
+      </c>
+      <c r="D94" t="s">
         <v>524</v>
       </c>
-      <c r="D94" t="s">
-        <v>525</v>
-      </c>
       <c r="E94" t="s">
         <v>25</v>
       </c>
       <c r="F94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G94" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H94" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="95" spans="2:8">
@@ -8381,22 +8381,22 @@
         <v>17</v>
       </c>
       <c r="C95" t="s">
+        <v>525</v>
+      </c>
+      <c r="D95" t="s">
         <v>526</v>
       </c>
-      <c r="D95" t="s">
-        <v>527</v>
-      </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G95" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H95" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="96" spans="2:8">
@@ -8404,22 +8404,22 @@
         <v>17</v>
       </c>
       <c r="C96" t="s">
+        <v>527</v>
+      </c>
+      <c r="D96" t="s">
         <v>528</v>
       </c>
-      <c r="D96" t="s">
-        <v>529</v>
-      </c>
       <c r="E96" t="s">
         <v>25</v>
       </c>
       <c r="F96" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G96" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H96" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="97" spans="2:8">
@@ -8427,22 +8427,22 @@
         <v>17</v>
       </c>
       <c r="C97" t="s">
+        <v>529</v>
+      </c>
+      <c r="D97" t="s">
         <v>530</v>
       </c>
-      <c r="D97" t="s">
-        <v>531</v>
-      </c>
       <c r="E97" t="s">
         <v>25</v>
       </c>
       <c r="F97" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G97" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H97" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="2:8">
@@ -8450,22 +8450,22 @@
         <v>17</v>
       </c>
       <c r="C98" t="s">
+        <v>531</v>
+      </c>
+      <c r="D98" t="s">
         <v>532</v>
       </c>
-      <c r="D98" t="s">
-        <v>533</v>
-      </c>
       <c r="E98" t="s">
         <v>25</v>
       </c>
       <c r="F98" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G98" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H98" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="2:8">
@@ -8473,22 +8473,22 @@
         <v>17</v>
       </c>
       <c r="C99" t="s">
+        <v>533</v>
+      </c>
+      <c r="D99" t="s">
         <v>534</v>
       </c>
-      <c r="D99" t="s">
-        <v>535</v>
-      </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G99" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H99" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -8496,22 +8496,22 @@
         <v>17</v>
       </c>
       <c r="C100" t="s">
+        <v>535</v>
+      </c>
+      <c r="D100" t="s">
         <v>536</v>
       </c>
-      <c r="D100" t="s">
-        <v>537</v>
-      </c>
       <c r="E100" t="s">
         <v>25</v>
       </c>
       <c r="F100" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G100" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H100" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="101" spans="2:8">
@@ -8519,22 +8519,22 @@
         <v>17</v>
       </c>
       <c r="C101" t="s">
+        <v>537</v>
+      </c>
+      <c r="D101" t="s">
         <v>538</v>
       </c>
-      <c r="D101" t="s">
-        <v>539</v>
-      </c>
       <c r="E101" t="s">
         <v>25</v>
       </c>
       <c r="F101" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G101" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H101" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="102" spans="2:8">
@@ -8542,22 +8542,22 @@
         <v>17</v>
       </c>
       <c r="C102" t="s">
+        <v>539</v>
+      </c>
+      <c r="D102" t="s">
         <v>540</v>
       </c>
-      <c r="D102" t="s">
-        <v>541</v>
-      </c>
       <c r="E102" t="s">
         <v>25</v>
       </c>
       <c r="F102" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G102" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H102" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -8565,22 +8565,22 @@
         <v>17</v>
       </c>
       <c r="C103" t="s">
+        <v>541</v>
+      </c>
+      <c r="D103" t="s">
         <v>542</v>
       </c>
-      <c r="D103" t="s">
-        <v>543</v>
-      </c>
       <c r="E103" t="s">
         <v>25</v>
       </c>
       <c r="F103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G103" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H103" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="104" spans="2:8">
@@ -8588,22 +8588,22 @@
         <v>17</v>
       </c>
       <c r="C104" t="s">
+        <v>543</v>
+      </c>
+      <c r="D104" t="s">
         <v>544</v>
       </c>
-      <c r="D104" t="s">
-        <v>545</v>
-      </c>
       <c r="E104" t="s">
         <v>25</v>
       </c>
       <c r="F104" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G104" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="105" spans="2:8">
@@ -8611,22 +8611,22 @@
         <v>17</v>
       </c>
       <c r="C105" t="s">
+        <v>545</v>
+      </c>
+      <c r="D105" t="s">
         <v>546</v>
       </c>
-      <c r="D105" t="s">
-        <v>547</v>
-      </c>
       <c r="E105" t="s">
         <v>25</v>
       </c>
       <c r="F105" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G105" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H105" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -8634,22 +8634,22 @@
         <v>17</v>
       </c>
       <c r="C106" t="s">
+        <v>547</v>
+      </c>
+      <c r="D106" t="s">
         <v>548</v>
       </c>
-      <c r="D106" t="s">
-        <v>549</v>
-      </c>
       <c r="E106" t="s">
         <v>25</v>
       </c>
       <c r="F106" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G106" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H106" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="107" spans="2:8">
@@ -8657,22 +8657,22 @@
         <v>17</v>
       </c>
       <c r="C107" t="s">
+        <v>549</v>
+      </c>
+      <c r="D107" t="s">
         <v>550</v>
       </c>
-      <c r="D107" t="s">
-        <v>551</v>
-      </c>
       <c r="E107" t="s">
         <v>25</v>
       </c>
       <c r="F107" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G107" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H107" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="108" spans="2:8">
@@ -8680,22 +8680,22 @@
         <v>17</v>
       </c>
       <c r="C108" t="s">
+        <v>551</v>
+      </c>
+      <c r="D108" t="s">
         <v>552</v>
       </c>
-      <c r="D108" t="s">
-        <v>553</v>
-      </c>
       <c r="E108" t="s">
         <v>25</v>
       </c>
       <c r="F108" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G108" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H108" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109" spans="2:8">
@@ -8703,22 +8703,22 @@
         <v>17</v>
       </c>
       <c r="C109" t="s">
+        <v>553</v>
+      </c>
+      <c r="D109" t="s">
         <v>554</v>
       </c>
-      <c r="D109" t="s">
-        <v>555</v>
-      </c>
       <c r="E109" t="s">
         <v>25</v>
       </c>
       <c r="F109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G109" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H109" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="110" spans="2:8">
@@ -8726,22 +8726,22 @@
         <v>17</v>
       </c>
       <c r="C110" t="s">
+        <v>555</v>
+      </c>
+      <c r="D110" t="s">
         <v>556</v>
       </c>
-      <c r="D110" t="s">
-        <v>557</v>
-      </c>
       <c r="E110" t="s">
         <v>25</v>
       </c>
       <c r="F110" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G110" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H110" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="111" spans="2:8">
@@ -8749,22 +8749,22 @@
         <v>17</v>
       </c>
       <c r="C111" t="s">
+        <v>557</v>
+      </c>
+      <c r="D111" t="s">
         <v>558</v>
       </c>
-      <c r="D111" t="s">
-        <v>559</v>
-      </c>
       <c r="E111" t="s">
         <v>25</v>
       </c>
       <c r="F111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G111" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H111" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="112" spans="2:8">
@@ -8772,22 +8772,22 @@
         <v>17</v>
       </c>
       <c r="C112" t="s">
+        <v>559</v>
+      </c>
+      <c r="D112" t="s">
         <v>560</v>
       </c>
-      <c r="D112" t="s">
-        <v>561</v>
-      </c>
       <c r="E112" t="s">
         <v>25</v>
       </c>
       <c r="F112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G112" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H112" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" spans="2:8">
@@ -8795,22 +8795,22 @@
         <v>17</v>
       </c>
       <c r="C113" t="s">
+        <v>561</v>
+      </c>
+      <c r="D113" t="s">
         <v>562</v>
       </c>
-      <c r="D113" t="s">
-        <v>563</v>
-      </c>
       <c r="E113" t="s">
         <v>25</v>
       </c>
       <c r="F113" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G113" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H113" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="114" spans="2:8">
@@ -8818,22 +8818,22 @@
         <v>17</v>
       </c>
       <c r="C114" t="s">
+        <v>563</v>
+      </c>
+      <c r="D114" t="s">
         <v>564</v>
       </c>
-      <c r="D114" t="s">
-        <v>565</v>
-      </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G114" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H114" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="115" spans="2:8">
@@ -8841,22 +8841,22 @@
         <v>17</v>
       </c>
       <c r="C115" t="s">
+        <v>565</v>
+      </c>
+      <c r="D115" t="s">
         <v>566</v>
       </c>
-      <c r="D115" t="s">
-        <v>567</v>
-      </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G115" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H115" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="116" spans="2:8">
@@ -8864,22 +8864,22 @@
         <v>17</v>
       </c>
       <c r="C116" t="s">
+        <v>567</v>
+      </c>
+      <c r="D116" t="s">
         <v>568</v>
       </c>
-      <c r="D116" t="s">
-        <v>569</v>
-      </c>
       <c r="E116" t="s">
         <v>25</v>
       </c>
       <c r="F116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G116" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="2:8">
@@ -8887,22 +8887,22 @@
         <v>17</v>
       </c>
       <c r="C117" t="s">
+        <v>569</v>
+      </c>
+      <c r="D117" t="s">
         <v>570</v>
       </c>
-      <c r="D117" t="s">
-        <v>571</v>
-      </c>
       <c r="E117" t="s">
         <v>25</v>
       </c>
       <c r="F117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G117" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="118" spans="2:8">
@@ -8910,22 +8910,22 @@
         <v>17</v>
       </c>
       <c r="C118" t="s">
+        <v>571</v>
+      </c>
+      <c r="D118" t="s">
         <v>572</v>
       </c>
-      <c r="D118" t="s">
-        <v>573</v>
-      </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="119" spans="2:8">
@@ -8933,22 +8933,22 @@
         <v>17</v>
       </c>
       <c r="C119" t="s">
+        <v>573</v>
+      </c>
+      <c r="D119" t="s">
         <v>574</v>
       </c>
-      <c r="D119" t="s">
-        <v>575</v>
-      </c>
       <c r="E119" t="s">
         <v>25</v>
       </c>
       <c r="F119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G119" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="120" spans="2:8">
@@ -8956,22 +8956,22 @@
         <v>17</v>
       </c>
       <c r="C120" t="s">
+        <v>575</v>
+      </c>
+      <c r="D120" t="s">
         <v>576</v>
       </c>
-      <c r="D120" t="s">
-        <v>577</v>
-      </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G120" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="121" spans="2:8">
@@ -8979,22 +8979,22 @@
         <v>17</v>
       </c>
       <c r="C121" t="s">
+        <v>577</v>
+      </c>
+      <c r="D121" t="s">
         <v>578</v>
       </c>
-      <c r="D121" t="s">
-        <v>579</v>
-      </c>
       <c r="E121" t="s">
         <v>25</v>
       </c>
       <c r="F121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G121" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H121" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="2:8">
@@ -9002,22 +9002,22 @@
         <v>17</v>
       </c>
       <c r="C122" t="s">
+        <v>579</v>
+      </c>
+      <c r="D122" t="s">
         <v>580</v>
       </c>
-      <c r="D122" t="s">
-        <v>581</v>
-      </c>
       <c r="E122" t="s">
         <v>25</v>
       </c>
       <c r="F122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G122" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H122" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="2:8">
@@ -9025,22 +9025,22 @@
         <v>17</v>
       </c>
       <c r="C123" t="s">
+        <v>581</v>
+      </c>
+      <c r="D123" t="s">
         <v>582</v>
       </c>
-      <c r="D123" t="s">
-        <v>583</v>
-      </c>
       <c r="E123" t="s">
         <v>25</v>
       </c>
       <c r="F123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G123" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H123" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="124" spans="2:8">
@@ -9048,22 +9048,22 @@
         <v>17</v>
       </c>
       <c r="C124" t="s">
+        <v>583</v>
+      </c>
+      <c r="D124" t="s">
         <v>584</v>
       </c>
-      <c r="D124" t="s">
-        <v>585</v>
-      </c>
       <c r="E124" t="s">
         <v>25</v>
       </c>
       <c r="F124" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G124" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H124" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="125" spans="2:8">
@@ -9071,22 +9071,22 @@
         <v>17</v>
       </c>
       <c r="C125" t="s">
+        <v>585</v>
+      </c>
+      <c r="D125" t="s">
         <v>586</v>
       </c>
-      <c r="D125" t="s">
-        <v>587</v>
-      </c>
       <c r="E125" t="s">
         <v>25</v>
       </c>
       <c r="F125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G125" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H125" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="2:8">
@@ -9094,22 +9094,22 @@
         <v>17</v>
       </c>
       <c r="C126" t="s">
+        <v>587</v>
+      </c>
+      <c r="D126" t="s">
         <v>588</v>
       </c>
-      <c r="D126" t="s">
-        <v>589</v>
-      </c>
       <c r="E126" t="s">
         <v>25</v>
       </c>
       <c r="F126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G126" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H126" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="127" spans="2:8">
@@ -9117,22 +9117,22 @@
         <v>17</v>
       </c>
       <c r="C127" t="s">
+        <v>589</v>
+      </c>
+      <c r="D127" t="s">
         <v>590</v>
       </c>
-      <c r="D127" t="s">
-        <v>591</v>
-      </c>
       <c r="E127" t="s">
         <v>25</v>
       </c>
       <c r="F127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G127" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H127" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="128" spans="2:8">
@@ -9140,22 +9140,22 @@
         <v>17</v>
       </c>
       <c r="C128" t="s">
+        <v>591</v>
+      </c>
+      <c r="D128" t="s">
         <v>592</v>
       </c>
-      <c r="D128" t="s">
-        <v>593</v>
-      </c>
       <c r="E128" t="s">
         <v>25</v>
       </c>
       <c r="F128" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G128" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H128" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="129" spans="2:8">
@@ -9163,22 +9163,22 @@
         <v>17</v>
       </c>
       <c r="C129" t="s">
+        <v>593</v>
+      </c>
+      <c r="D129" t="s">
         <v>594</v>
       </c>
-      <c r="D129" t="s">
-        <v>595</v>
-      </c>
       <c r="E129" t="s">
         <v>25</v>
       </c>
       <c r="F129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G129" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H129" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="130" spans="2:8">
@@ -9186,22 +9186,22 @@
         <v>17</v>
       </c>
       <c r="C130" t="s">
+        <v>595</v>
+      </c>
+      <c r="D130" t="s">
         <v>596</v>
       </c>
-      <c r="D130" t="s">
-        <v>597</v>
-      </c>
       <c r="E130" t="s">
         <v>25</v>
       </c>
       <c r="F130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G130" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H130" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -9257,7 +9257,7 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -9265,42 +9265,42 @@
     </row>
     <row r="5" spans="2:12">
       <c r="B5" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="H5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="I5" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="K5" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="L5" s="15" t="s">
         <v>58</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="6" spans="2:12">
       <c r="D6" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" s="11">
         <v>0</v>
@@ -9311,7 +9311,7 @@
     </row>
     <row r="7" spans="2:12">
       <c r="D7" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" s="11">
         <v>0</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="8" spans="2:12">
       <c r="D8" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" s="11">
         <v>0</v>
@@ -9333,7 +9333,7 @@
     </row>
     <row r="9" spans="2:12">
       <c r="D9" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E9" s="11">
         <v>0</v>
@@ -9344,7 +9344,7 @@
     </row>
     <row r="10" spans="2:12">
       <c r="D10" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E10" s="11">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     </row>
     <row r="11" spans="2:12">
       <c r="D11" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E11" s="11">
         <v>0</v>
@@ -9366,7 +9366,7 @@
     </row>
     <row r="14" spans="2:12">
       <c r="B14" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
@@ -9374,50 +9374,50 @@
     </row>
     <row r="15" spans="2:12">
       <c r="B15" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>51</v>
-      </c>
       <c r="E15" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>65</v>
-      </c>
       <c r="H15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="15" t="s">
         <v>55</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="2:12">
       <c r="D16" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" s="11">
         <v>2222</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:14">
       <c r="D17" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F17" s="11">
         <v>8888</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="12.75">
@@ -9814,13 +9814,13 @@
     <row r="2" spans="1:14" ht="17.649999999999999" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -9828,44 +9828,44 @@
     <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I3" s="4">
         <v>2022</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="13.15">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="6"/>
       <c r="F4" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I4" s="11">
         <v>0.05</v>
@@ -9874,10 +9874,10 @@
         <v>25</v>
       </c>
       <c r="L4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="N4" s="6">
         <v>1055.55</v>
@@ -9886,13 +9886,13 @@
     <row r="5" spans="1:14" ht="13.15">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>187</v>
       </c>
       <c r="I5" s="11">
         <v>1</v>
@@ -9901,10 +9901,10 @@
         <v>25</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="6">
         <v>3.6</v>
@@ -9913,19 +9913,19 @@
     <row r="6" spans="1:14" ht="13.15">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I6" s="11">
         <v>2025</v>
       </c>
       <c r="L6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="N6" s="6">
         <v>1000</v>
@@ -9934,19 +9934,19 @@
     <row r="7" spans="1:14" ht="13.15">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I7" s="11">
         <v>1</v>
       </c>
       <c r="L7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="N7" s="6">
         <v>1000</v>
@@ -9955,25 +9955,25 @@
     <row r="8" spans="1:14" ht="13.15">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I8" s="11">
         <v>2.2201</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N8" s="6">
         <v>1.05555</v>
@@ -9982,25 +9982,25 @@
     <row r="9" spans="1:14" ht="13.15">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I9" s="11">
         <v>2.1427</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N9" s="6">
         <v>4.1868000000000002E-2</v>
@@ -10009,25 +10009,25 @@
     <row r="10" spans="1:14" ht="13.15">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I10" s="11">
         <v>2.077</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N10" s="6">
         <v>41.868000000000002</v>
@@ -10036,25 +10036,25 @@
     <row r="11" spans="1:14" ht="13.15">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I11" s="11">
         <v>2.0358000000000001</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N11" s="6">
         <v>3.5999999999999999E-3</v>
@@ -10063,25 +10063,25 @@
     <row r="12" spans="1:14" ht="13.15">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I12" s="11">
         <v>1.9870000000000001</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N12" s="6">
         <v>1000000</v>
@@ -10090,25 +10090,25 @@
     <row r="13" spans="1:14" ht="13.15">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I13" s="11">
         <v>1.9192</v>
       </c>
       <c r="L13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="N13" s="6">
         <v>1000</v>
@@ -10117,25 +10117,25 @@
     <row r="14" spans="1:14" ht="13.15">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I14" s="11">
         <v>1.8468</v>
       </c>
       <c r="L14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="N14" s="6">
         <v>5.8615199999999996</v>
@@ -10144,25 +10144,25 @@
     <row r="15" spans="1:14" ht="13.15">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I15" s="11">
         <v>1.7799</v>
       </c>
       <c r="L15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="N15" s="6">
         <v>1E-3</v>
@@ -10171,25 +10171,25 @@
     <row r="16" spans="1:14" ht="13.15">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I16" s="11">
         <v>1.722</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N16" s="6">
         <v>1000</v>
@@ -10198,25 +10198,25 @@
     <row r="17" spans="1:14" ht="13.15">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I17" s="11">
         <v>1.6836</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N17" s="6">
         <v>37.68</v>
@@ -10224,25 +10224,25 @@
     </row>
     <row r="18" spans="1:14" ht="13.15">
       <c r="B18" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I18" s="11">
         <v>1.6446000000000001</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N18" s="6">
         <v>2139.4548</v>
@@ -10250,25 +10250,25 @@
     </row>
     <row r="19" spans="1:14" ht="13.15">
       <c r="B19" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I19" s="11">
         <v>1.6102000000000001</v>
       </c>
       <c r="L19" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M19" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="N19" s="6">
         <v>2.78</v>
@@ -10276,25 +10276,25 @@
     </row>
     <row r="20" spans="1:14" ht="13.15">
       <c r="B20" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I20" s="11">
         <v>1.5770999999999999</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N20" s="6">
         <v>3.6</v>
@@ -10302,25 +10302,25 @@
     </row>
     <row r="21" spans="1:14" ht="13.15">
       <c r="B21" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I21" s="11">
         <v>1.5488</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
@@ -10328,25 +10328,25 @@
     </row>
     <row r="22" spans="1:14" ht="13.15">
       <c r="B22" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I22" s="11">
         <v>1.5224</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N22" s="6">
         <v>31.536000000000001</v>
@@ -10354,25 +10354,25 @@
     </row>
     <row r="23" spans="1:14" ht="13.15">
       <c r="B23" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I23" s="11">
         <v>1.5058</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N23" s="6">
         <v>120</v>
@@ -10380,25 +10380,25 @@
     </row>
     <row r="24" spans="1:14" ht="13.15">
       <c r="B24" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I24" s="11">
         <v>1.4844999999999999</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N24" s="11">
         <v>5.8615199999999996</v>
@@ -10406,25 +10406,25 @@
     </row>
     <row r="25" spans="1:14" ht="13.15">
       <c r="B25" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I25" s="11">
         <v>1.4518</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N25" s="11">
         <v>54</v>
@@ -10432,16 +10432,16 @@
     </row>
     <row r="26" spans="1:14" ht="13.15">
       <c r="B26" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I26" s="11">
         <v>1.4198999999999999</v>
@@ -10449,16 +10449,16 @@
     </row>
     <row r="27" spans="1:14" ht="13.15">
       <c r="B27" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I27" s="11">
         <v>1.3986000000000001</v>
@@ -10466,16 +10466,16 @@
     </row>
     <row r="28" spans="1:14" ht="13.15">
       <c r="B28" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I28" s="11">
         <v>1.3727</v>
@@ -10483,16 +10483,16 @@
     </row>
     <row r="29" spans="1:14" ht="13.15">
       <c r="B29" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I29" s="11">
         <v>1.3369</v>
@@ -10500,16 +10500,16 @@
     </row>
     <row r="30" spans="1:14" ht="13.15">
       <c r="B30" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I30" s="11">
         <v>1.2967</v>
@@ -10517,16 +10517,16 @@
     </row>
     <row r="31" spans="1:14" ht="13.15">
       <c r="B31" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I31" s="11">
         <v>1.2583</v>
@@ -10534,16 +10534,16 @@
     </row>
     <row r="32" spans="1:14" ht="13.15">
       <c r="B32" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I32" s="11">
         <v>1.2253000000000001</v>
@@ -10551,16 +10551,16 @@
     </row>
     <row r="33" spans="2:9" ht="13.15">
       <c r="B33" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I33" s="11">
         <v>1.2023999999999999</v>
@@ -10568,16 +10568,16 @@
     </row>
     <row r="34" spans="2:9" ht="13.15">
       <c r="B34" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I34" s="11">
         <v>1.1931</v>
@@ -10585,16 +10585,16 @@
     </row>
     <row r="35" spans="2:9" ht="13.15">
       <c r="B35" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I35" s="11">
         <v>1.1793</v>
@@ -10602,16 +10602,16 @@
     </row>
     <row r="36" spans="2:9" ht="13.15">
       <c r="B36" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I36" s="11">
         <v>1.1552</v>
@@ -10619,16 +10619,16 @@
     </row>
     <row r="37" spans="2:9" ht="13.15">
       <c r="B37" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I37" s="11">
         <v>1.1334</v>
@@ -10636,16 +10636,16 @@
     </row>
     <row r="38" spans="2:9" ht="13.15">
       <c r="B38" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I38" s="11">
         <v>1.1136999999999999</v>
@@ -10653,16 +10653,16 @@
     </row>
     <row r="39" spans="2:9" ht="13.15">
       <c r="B39" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I39" s="11">
         <v>1.0934999999999999</v>
@@ -10670,16 +10670,16 @@
     </row>
     <row r="40" spans="2:9" ht="13.15">
       <c r="B40" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I40" s="11">
         <v>1.0831</v>
@@ -10687,16 +10687,16 @@
     </row>
     <row r="41" spans="2:9" ht="13.15">
       <c r="B41" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I41" s="11">
         <v>1.0719000000000001</v>
@@ -10704,16 +10704,16 @@
     </row>
     <row r="42" spans="2:9" ht="13.15">
       <c r="B42" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I42" s="11">
         <v>1.0519000000000001</v>
@@ -10721,16 +10721,16 @@
     </row>
     <row r="43" spans="2:9" ht="13.15">
       <c r="B43" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I43" s="11">
         <v>1.0274000000000001</v>
@@ -10738,16 +10738,16 @@
     </row>
     <row r="44" spans="2:9" ht="13.15">
       <c r="B44" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I44" s="11">
         <v>1.0091000000000001</v>
@@ -10755,16 +10755,16 @@
     </row>
     <row r="45" spans="2:9" ht="13.15">
       <c r="B45" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I45" s="11">
         <v>1</v>
@@ -10772,16 +10772,16 @@
     </row>
     <row r="46" spans="2:9" ht="13.15">
       <c r="B46" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I46" s="11">
         <v>0.98960000000000004</v>
@@ -10789,16 +10789,16 @@
     </row>
     <row r="47" spans="2:9" ht="13.15">
       <c r="B47" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I47" s="11">
         <v>0.97809999999999997</v>
@@ -10806,16 +10806,16 @@
     </row>
     <row r="48" spans="2:9" ht="13.15">
       <c r="B48" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I48" s="11">
         <v>0.96499999999999997</v>
@@ -10823,16 +10823,16 @@
     </row>
     <row r="49" spans="2:9" ht="13.15">
       <c r="B49" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I49" s="11">
         <v>0.94910000000000005</v>
@@ -10840,16 +10840,16 @@
     </row>
     <row r="50" spans="2:9" ht="13.15">
       <c r="B50" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I50" s="11">
         <v>0.92969999999999997</v>
@@ -10857,7 +10857,7 @@
     </row>
     <row r="51" spans="2:9" ht="13.15">
       <c r="B51" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F51" s="11" t="str">
         <f>F46</f>
@@ -10868,7 +10868,7 @@
         <v>USD20</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I51" s="11">
         <f t="shared" si="0"/>
@@ -10877,13 +10877,13 @@
     </row>
     <row r="52" spans="2:9" ht="13.15">
       <c r="B52" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I52" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10891,13 +10891,13 @@
     </row>
     <row r="53" spans="2:9" ht="13.15">
       <c r="B53" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I53" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10905,13 +10905,13 @@
     </row>
     <row r="54" spans="2:9" ht="13.15">
       <c r="B54" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I54" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10919,10 +10919,10 @@
     </row>
     <row r="55" spans="2:9">
       <c r="F55" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I55" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10930,10 +10930,10 @@
     </row>
     <row r="56" spans="2:9">
       <c r="F56" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I56" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10941,10 +10941,10 @@
     </row>
     <row r="57" spans="2:9">
       <c r="F57" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I57" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10952,10 +10952,10 @@
     </row>
     <row r="58" spans="2:9">
       <c r="F58" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I58" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10963,10 +10963,10 @@
     </row>
     <row r="59" spans="2:9">
       <c r="F59" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I59" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="60" spans="2:9">
       <c r="F60" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I60" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10985,10 +10985,10 @@
     </row>
     <row r="61" spans="2:9">
       <c r="F61" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I61" s="11">
         <v>7.0000000000000007E-2</v>
@@ -10996,10 +10996,10 @@
     </row>
     <row r="62" spans="2:9">
       <c r="F62" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I62" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11007,10 +11007,10 @@
     </row>
     <row r="63" spans="2:9">
       <c r="F63" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I63" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11018,10 +11018,10 @@
     </row>
     <row r="64" spans="2:9">
       <c r="F64" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I64" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11029,10 +11029,10 @@
     </row>
     <row r="65" spans="6:9">
       <c r="F65" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I65" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11040,10 +11040,10 @@
     </row>
     <row r="66" spans="6:9">
       <c r="F66" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I66" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11051,10 +11051,10 @@
     </row>
     <row r="67" spans="6:9">
       <c r="F67" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I67" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11062,10 +11062,10 @@
     </row>
     <row r="68" spans="6:9">
       <c r="F68" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I68" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="69" spans="6:9">
       <c r="F69" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I69" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11084,10 +11084,10 @@
     </row>
     <row r="70" spans="6:9">
       <c r="F70" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I70" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11095,10 +11095,10 @@
     </row>
     <row r="71" spans="6:9">
       <c r="F71" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I71" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11106,10 +11106,10 @@
     </row>
     <row r="72" spans="6:9">
       <c r="F72" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I72" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11117,10 +11117,10 @@
     </row>
     <row r="73" spans="6:9">
       <c r="F73" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I73" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="74" spans="6:9">
       <c r="F74" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I74" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11139,10 +11139,10 @@
     </row>
     <row r="75" spans="6:9">
       <c r="F75" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I75" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11150,10 +11150,10 @@
     </row>
     <row r="76" spans="6:9">
       <c r="F76" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I76" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11161,10 +11161,10 @@
     </row>
     <row r="77" spans="6:9">
       <c r="F77" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I77" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11172,10 +11172,10 @@
     </row>
     <row r="78" spans="6:9">
       <c r="F78" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I78" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11183,10 +11183,10 @@
     </row>
     <row r="79" spans="6:9">
       <c r="F79" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I79" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11194,10 +11194,10 @@
     </row>
     <row r="80" spans="6:9">
       <c r="F80" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I80" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11205,10 +11205,10 @@
     </row>
     <row r="81" spans="6:9">
       <c r="F81" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I81" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11216,10 +11216,10 @@
     </row>
     <row r="82" spans="6:9">
       <c r="F82" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I82" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11227,10 +11227,10 @@
     </row>
     <row r="83" spans="6:9">
       <c r="F83" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I83" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11238,10 +11238,10 @@
     </row>
     <row r="84" spans="6:9">
       <c r="F84" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I84" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11249,10 +11249,10 @@
     </row>
     <row r="85" spans="6:9">
       <c r="F85" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I85" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11260,10 +11260,10 @@
     </row>
     <row r="86" spans="6:9">
       <c r="F86" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I86" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11271,10 +11271,10 @@
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I87" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11282,10 +11282,10 @@
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I88" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11293,10 +11293,10 @@
     </row>
     <row r="89" spans="6:9">
       <c r="F89" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I89" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11304,10 +11304,10 @@
     </row>
     <row r="90" spans="6:9">
       <c r="F90" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I90" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11315,10 +11315,10 @@
     </row>
     <row r="91" spans="6:9">
       <c r="F91" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I91" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11326,10 +11326,10 @@
     </row>
     <row r="92" spans="6:9">
       <c r="F92" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I92" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11337,10 +11337,10 @@
     </row>
     <row r="93" spans="6:9">
       <c r="F93" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I93" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11348,10 +11348,10 @@
     </row>
     <row r="94" spans="6:9">
       <c r="F94" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I94" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="95" spans="6:9">
       <c r="F95" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H95" s="11" t="str">
         <f>H51</f>
@@ -11371,39 +11371,39 @@
     </row>
     <row r="99" spans="5:10" ht="17.649999999999999" thickBot="1">
       <c r="E99" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I100" s="4">
         <v>2022</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="5:10" ht="14.25">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H101" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I101" s="22">
         <f>1.10926234054354*I40</f>
@@ -11413,11 +11413,11 @@
     <row r="102" spans="5:10" ht="14.25">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G102"/>
       <c r="H102" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I102" s="22">
         <f>I84</f>
@@ -11442,26 +11442,26 @@
   <sheetData>
     <row r="3" spans="2:4" ht="17.649999999999999" thickBot="1">
       <c r="B3" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="D5" s="6">
         <v>-1</v>
@@ -11469,10 +11469,10 @@
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -11480,10 +11480,10 @@
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -11491,10 +11491,10 @@
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -11513,10 +11513,10 @@
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -11524,10 +11524,10 @@
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
@@ -11535,10 +11535,10 @@
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -11546,10 +11546,10 @@
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
@@ -11568,10 +11568,10 @@
     </row>
     <row r="15" spans="2:4">
       <c r="B15" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -11579,10 +11579,10 @@
     </row>
     <row r="16" spans="2:4">
       <c r="B16" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D16" s="16">
         <v>1.0000000000000001E-5</v>
@@ -11590,10 +11590,10 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D17" s="16">
         <v>1.0000000000000001E-5</v>
@@ -11601,10 +11601,10 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D18" s="16">
         <v>1.0000000000000001E-5</v>
@@ -11612,10 +11612,10 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D19" s="16">
         <v>1.0000000000000001E-5</v>
@@ -11623,10 +11623,10 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="D20" s="17">
         <v>1</v>
@@ -11634,73 +11634,73 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="17.649999999999999" thickBot="1">
       <c r="B25" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="27" spans="2:4">
       <c r="B27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E67D5B1-F520-4CF6-8C13-66DD34CB87E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B962C04B-8237-42E0-B8D2-1BFDDE737928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="607">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1839,15 +1839,6 @@
   </si>
   <si>
     <t>Unit</t>
-  </si>
-  <si>
-    <t>Sub type</t>
-  </si>
-  <si>
-    <t>Lim type</t>
-  </si>
-  <si>
-    <t>Time slice level</t>
   </si>
   <si>
     <t>AGRELC</t>
@@ -4743,7 +4734,7 @@
     </row>
     <row r="17" spans="2:18">
       <c r="B17" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C17" t="s">
         <v>202</v>
@@ -4775,7 +4766,7 @@
     </row>
     <row r="18" spans="2:18">
       <c r="B18" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -4807,7 +4798,7 @@
     </row>
     <row r="19" spans="2:18">
       <c r="B19" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
@@ -4839,7 +4830,7 @@
     </row>
     <row r="20" spans="2:18">
       <c r="B20" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
@@ -4871,7 +4862,7 @@
     </row>
     <row r="21" spans="2:18">
       <c r="B21" t="s">
-        <v>609</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
         <v>196</v>
@@ -5076,13 +5067,13 @@
         <v>599</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>601</v>
+        <v>15</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>602</v>
+        <v>13</v>
       </c>
       <c r="M28" t="s">
         <v>17</v>
@@ -5108,7 +5099,7 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E29" t="s">
         <v>84</v>
@@ -5117,7 +5108,7 @@
         <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="M29" t="s">
         <v>17</v>
@@ -5143,7 +5134,7 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E30" t="s">
         <v>84</v>
@@ -5152,7 +5143,7 @@
         <v>37</v>
       </c>
       <c r="H30" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="M30" t="s">
         <v>17</v>
@@ -5178,7 +5169,7 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E31" t="s">
         <v>84</v>
@@ -5187,7 +5178,7 @@
         <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="M31" t="s">
         <v>17</v>
@@ -5213,7 +5204,7 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E32" t="s">
         <v>84</v>
@@ -5222,7 +5213,7 @@
         <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="M32" t="s">
         <v>17</v>
@@ -5248,7 +5239,7 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E33" t="s">
         <v>84</v>
@@ -5257,7 +5248,7 @@
         <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="M33" t="s">
         <v>17</v>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B962C04B-8237-42E0-B8D2-1BFDDE737928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C288AC-7D38-495D-85D7-47AE3E824F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="618">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1860,6 +1860,39 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t>PhaseII</t>
+  </si>
+  <si>
+    <t>Phase1</t>
+  </si>
+  <si>
+    <t>year2</t>
+  </si>
+  <si>
+    <t>Pset_Set</t>
+  </si>
+  <si>
+    <t>UP,LO</t>
+  </si>
+  <si>
+    <t>ACT_BND</t>
+  </si>
+  <si>
+    <t>MIN,PRE,IMP,EXP,-ELE,-DMD</t>
+  </si>
+  <si>
+    <t>Share-O</t>
+  </si>
+  <si>
+    <t>Share-I</t>
+  </si>
+  <si>
+    <t>DMD</t>
+  </si>
+  <si>
+    <t>R*,C*</t>
   </si>
 </sst>
 </file>
@@ -5979,7 +6012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
-  <dimension ref="B3:G33"/>
+  <dimension ref="B3:J33"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.1328125" style="6" customWidth="1"/>
@@ -5991,35 +6024,38 @@
     <col min="8" max="16384" width="11.3984375" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:10">
       <c r="B3" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:10">
       <c r="B4" s="6">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
       <c r="B7" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:10">
       <c r="B8" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="2:10">
       <c r="B11" s="6" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="2:7" ht="14.25">
+      <c r="I11" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="14.25">
       <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
@@ -6028,26 +6064,38 @@
       </c>
       <c r="E12" s="8" t="str">
         <f>"msy"&amp;COUNT(E14:E46)&amp;"_"&amp;MAX(E14:E46)</f>
-        <v>msy7_2050</v>
+        <v>msy7_2046</v>
       </c>
       <c r="F12" s="8" t="str">
         <f t="shared" ref="F12:G12" si="0">"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
-        <v>msy6_2050</v>
+        <v>msy6_2046</v>
       </c>
       <c r="G12" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>msy5_2050</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="14.25">
+        <v>msy5_2046</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="14.25">
       <c r="B13" s="9">
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="2:7" ht="14.25">
+      <c r="I13" s="6">
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="14.25">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -6056,18 +6104,24 @@
       </c>
       <c r="E14" s="6">
         <f t="shared" ref="E14:G14" si="1">$B$4</f>
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="F14" s="6">
         <f t="shared" si="1"/>
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="G14" s="6">
         <f t="shared" si="1"/>
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="14.25">
+        <v>2018</v>
+      </c>
+      <c r="I14" s="6">
+        <v>2</v>
+      </c>
+      <c r="J14" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="14.25">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -6076,18 +6130,24 @@
       </c>
       <c r="E15" s="6">
         <f>E14+3</f>
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F15" s="6">
         <f>F14+3</f>
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="G15" s="6">
         <f>G14+3</f>
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="14.25">
+        <v>2021</v>
+      </c>
+      <c r="I15" s="6">
+        <v>5</v>
+      </c>
+      <c r="J15" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="14.25">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -6096,18 +6156,24 @@
       </c>
       <c r="E16" s="6">
         <f>E15+5</f>
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="F16" s="6">
         <f>F15+5</f>
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="G16" s="6">
         <f>G15+5</f>
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="14.25">
+        <v>2026</v>
+      </c>
+      <c r="I16" s="6">
+        <v>5</v>
+      </c>
+      <c r="J16" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="14.25">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -6116,18 +6182,24 @@
       </c>
       <c r="E17" s="6">
         <f t="shared" ref="E17:E20" si="2">E16+5</f>
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="F17" s="6">
         <f>F16+5</f>
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="G17" s="6">
         <f>G16+10</f>
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="14.25">
+        <v>2036</v>
+      </c>
+      <c r="I17" s="6">
+        <v>5</v>
+      </c>
+      <c r="J17" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="14.25">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -6136,18 +6208,24 @@
       </c>
       <c r="E18" s="6">
         <f t="shared" si="2"/>
-        <v>2040</v>
+        <v>2036</v>
       </c>
       <c r="F18" s="6">
         <f>F17+5</f>
-        <v>2040</v>
+        <v>2036</v>
       </c>
       <c r="G18" s="6">
         <f t="shared" ref="G18" si="3">G17+10</f>
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="14.25">
+        <v>2046</v>
+      </c>
+      <c r="I18" s="6">
+        <v>5</v>
+      </c>
+      <c r="J18" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="14.25">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -6156,14 +6234,20 @@
       </c>
       <c r="E19" s="6">
         <f t="shared" si="2"/>
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="F19" s="6">
         <f>F18+10</f>
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="14.25">
+        <v>2046</v>
+      </c>
+      <c r="I19" s="6">
+        <v>5</v>
+      </c>
+      <c r="J19" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="14.25">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -6172,34 +6256,55 @@
       </c>
       <c r="E20" s="6">
         <f t="shared" si="2"/>
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="14.25">
+        <v>2046</v>
+      </c>
+      <c r="I20" s="6">
+        <v>5</v>
+      </c>
+      <c r="J20" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="14.25">
       <c r="B21" s="9">
         <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="22" spans="2:7" ht="14.25">
+      <c r="I21" s="6">
+        <v>5</v>
+      </c>
+      <c r="J21" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="14.25">
       <c r="B22" s="9">
         <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="23" spans="2:7" ht="14.25">
+      <c r="I22" s="6">
+        <v>5</v>
+      </c>
+      <c r="J22" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" ht="14.25">
       <c r="B23" s="9">
         <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="24" spans="2:7" ht="14.25">
+      <c r="I23" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="14.25">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -6207,43 +6312,43 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.25">
+    <row r="25" spans="2:10" ht="14.25">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.25">
+    <row r="26" spans="2:10" ht="14.25">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.25">
+    <row r="27" spans="2:10" ht="14.25">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.25">
+    <row r="28" spans="2:10" ht="14.25">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.25">
+    <row r="29" spans="2:10" ht="14.25">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.25">
+    <row r="30" spans="2:10" ht="14.25">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="2:7" ht="14.25">
+    <row r="31" spans="2:10" ht="14.25">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="14.25">
+    <row r="32" spans="2:10" ht="14.25">
       <c r="B32" s="9"/>
     </row>
     <row r="33" spans="2:2" ht="14.25">
@@ -9202,7 +9307,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N42"/>
+  <dimension ref="B1:AA42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
@@ -9220,11 +9325,11 @@
     <col min="13" max="16384" width="11.3984375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.75">
+    <row r="1" spans="2:27" ht="12.75">
       <c r="B1" s="6"/>
       <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="2:12" ht="12.75">
+    <row r="2" spans="2:27" ht="12.75">
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -9235,7 +9340,7 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
     </row>
-    <row r="3" spans="2:12" ht="12.75">
+    <row r="3" spans="2:27" ht="12.75">
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -9246,15 +9351,18 @@
       <c r="I3" s="13"/>
       <c r="J3" s="13"/>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:27">
       <c r="B4" s="14" t="s">
         <v>47</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="2:12">
+      <c r="N4" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" ht="14.25">
       <c r="B5" s="15" t="s">
         <v>48</v>
       </c>
@@ -9288,8 +9396,36 @@
       <c r="L5" s="15" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" spans="2:12">
+      <c r="N5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+    </row>
+    <row r="6" spans="2:27" ht="14.25">
       <c r="D6" s="11" t="s">
         <v>59</v>
       </c>
@@ -9299,8 +9435,30 @@
       <c r="F6" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="2:12">
+      <c r="O6" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
+        <v>5</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+    </row>
+    <row r="7" spans="2:27" ht="14.25">
       <c r="D7" s="11" t="s">
         <v>60</v>
       </c>
@@ -9310,8 +9468,30 @@
       <c r="F7" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="2:12">
+      <c r="O7" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>0</v>
+      </c>
+      <c r="R7" s="11">
+        <v>3</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>606</v>
+      </c>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+    </row>
+    <row r="8" spans="2:27" ht="14.25">
       <c r="D8" s="11" t="s">
         <v>61</v>
       </c>
@@ -9321,8 +9501,30 @@
       <c r="F8" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="2:12">
+      <c r="O8" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>3</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>606</v>
+      </c>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+    </row>
+    <row r="9" spans="2:27">
       <c r="D9" s="11" t="s">
         <v>198</v>
       </c>
@@ -9332,8 +9534,26 @@
       <c r="F9" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="2:12">
+      <c r="O9" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="10" spans="2:27">
       <c r="D10" s="11" t="s">
         <v>201</v>
       </c>
@@ -9344,7 +9564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11" spans="2:27">
       <c r="D11" s="11" t="s">
         <v>211</v>
       </c>
@@ -9355,7 +9575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:27">
       <c r="B14" s="14" t="s">
         <v>62</v>
       </c>
@@ -9363,7 +9583,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:27">
       <c r="B15" s="15" t="s">
         <v>48</v>
       </c>
@@ -9389,7 +9609,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:27">
       <c r="D16" s="11" t="s">
         <v>65</v>
       </c>
@@ -9422,7 +9642,7 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="2:14" ht="12.75">
+    <row r="19" spans="2:14" ht="14.25">
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -9432,8 +9652,9 @@
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
-    </row>
-    <row r="20" spans="2:14" ht="12.75">
+      <c r="N19"/>
+    </row>
+    <row r="20" spans="2:14" ht="14.25">
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -9443,6 +9664,7 @@
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
+      <c r="N20"/>
     </row>
     <row r="21" spans="2:14" ht="14.25">
       <c r="B21"/>
@@ -9757,7 +9979,6 @@
       <c r="K41"/>
       <c r="L41"/>
       <c r="M41"/>
-      <c r="N41"/>
     </row>
     <row r="42" spans="2:14" ht="14.25">
       <c r="B42"/>
@@ -9772,7 +9993,6 @@
       <c r="K42"/>
       <c r="L42"/>
       <c r="M42"/>
-      <c r="N42"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C288AC-7D38-495D-85D7-47AE3E824F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6B2E8B-A7AE-4812-A565-A6F4D792DE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="619">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1893,6 +1893,9 @@
   </si>
   <si>
     <t>R*,C*</t>
+  </si>
+  <si>
+    <t>MioNZDollar</t>
   </si>
 </sst>
 </file>
@@ -10003,7 +10006,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
-  <dimension ref="A2:N102"/>
+  <dimension ref="A2:N104"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
@@ -10012,7 +10015,7 @@
     <col min="5" max="5" width="13.53125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.53125" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.3984375" style="11"/>
@@ -10069,17 +10072,17 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.15">
+    <row r="4" spans="1:14" ht="12.75">
       <c r="A4" s="13"/>
-      <c r="B4" s="19" t="s">
-        <v>134</v>
+      <c r="B4" s="11" t="s">
+        <v>618</v>
       </c>
       <c r="C4" s="6"/>
       <c r="F4" s="11" t="s">
         <v>184</v>
       </c>
       <c r="I4" s="11">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>25</v>
@@ -10097,7 +10100,7 @@
     <row r="5" spans="1:14" ht="13.15">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>185</v>
@@ -10124,7 +10127,7 @@
     <row r="6" spans="1:14" ht="13.15">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>187</v>
@@ -10145,7 +10148,7 @@
     <row r="7" spans="1:14" ht="13.15">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>188</v>
@@ -10166,7 +10169,7 @@
     <row r="8" spans="1:14" ht="13.15">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>189</v>
@@ -10193,7 +10196,7 @@
     <row r="9" spans="1:14" ht="13.15">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>189</v>
@@ -10220,7 +10223,7 @@
     <row r="10" spans="1:14" ht="13.15">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>189</v>
@@ -10247,7 +10250,7 @@
     <row r="11" spans="1:14" ht="13.15">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>189</v>
@@ -10274,7 +10277,7 @@
     <row r="12" spans="1:14" ht="13.15">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>189</v>
@@ -10301,7 +10304,7 @@
     <row r="13" spans="1:14" ht="13.15">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>189</v>
@@ -10328,7 +10331,7 @@
     <row r="14" spans="1:14" ht="13.15">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>189</v>
@@ -10355,7 +10358,7 @@
     <row r="15" spans="1:14" ht="13.15">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>189</v>
@@ -10382,7 +10385,7 @@
     <row r="16" spans="1:14" ht="13.15">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>189</v>
@@ -10409,7 +10412,7 @@
     <row r="17" spans="1:14" ht="13.15">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>189</v>
@@ -10435,7 +10438,7 @@
     </row>
     <row r="18" spans="1:14" ht="13.15">
       <c r="B18" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>189</v>
@@ -10461,7 +10464,7 @@
     </row>
     <row r="19" spans="1:14" ht="13.15">
       <c r="B19" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>189</v>
@@ -10487,7 +10490,7 @@
     </row>
     <row r="20" spans="1:14" ht="13.15">
       <c r="B20" s="19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>189</v>
@@ -10513,7 +10516,7 @@
     </row>
     <row r="21" spans="1:14" ht="13.15">
       <c r="B21" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>189</v>
@@ -10539,7 +10542,7 @@
     </row>
     <row r="22" spans="1:14" ht="13.15">
       <c r="B22" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>189</v>
@@ -10565,7 +10568,7 @@
     </row>
     <row r="23" spans="1:14" ht="13.15">
       <c r="B23" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>189</v>
@@ -10591,7 +10594,7 @@
     </row>
     <row r="24" spans="1:14" ht="13.15">
       <c r="B24" s="19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>189</v>
@@ -10617,7 +10620,7 @@
     </row>
     <row r="25" spans="1:14" ht="13.15">
       <c r="B25" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>189</v>
@@ -10643,7 +10646,7 @@
     </row>
     <row r="26" spans="1:14" ht="13.15">
       <c r="B26" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>189</v>
@@ -10660,7 +10663,7 @@
     </row>
     <row r="27" spans="1:14" ht="13.15">
       <c r="B27" s="19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>189</v>
@@ -10677,7 +10680,7 @@
     </row>
     <row r="28" spans="1:14" ht="13.15">
       <c r="B28" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>189</v>
@@ -10694,7 +10697,7 @@
     </row>
     <row r="29" spans="1:14" ht="13.15">
       <c r="B29" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>189</v>
@@ -10711,7 +10714,7 @@
     </row>
     <row r="30" spans="1:14" ht="13.15">
       <c r="B30" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>189</v>
@@ -10728,7 +10731,7 @@
     </row>
     <row r="31" spans="1:14" ht="13.15">
       <c r="B31" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>189</v>
@@ -10745,7 +10748,7 @@
     </row>
     <row r="32" spans="1:14" ht="13.15">
       <c r="B32" s="19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>189</v>
@@ -10762,7 +10765,7 @@
     </row>
     <row r="33" spans="2:9" ht="13.15">
       <c r="B33" s="19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>189</v>
@@ -10779,7 +10782,7 @@
     </row>
     <row r="34" spans="2:9" ht="13.15">
       <c r="B34" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>189</v>
@@ -10796,7 +10799,7 @@
     </row>
     <row r="35" spans="2:9" ht="13.15">
       <c r="B35" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>189</v>
@@ -10813,7 +10816,7 @@
     </row>
     <row r="36" spans="2:9" ht="13.15">
       <c r="B36" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>189</v>
@@ -10830,7 +10833,7 @@
     </row>
     <row r="37" spans="2:9" ht="13.15">
       <c r="B37" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>189</v>
@@ -10847,7 +10850,7 @@
     </row>
     <row r="38" spans="2:9" ht="13.15">
       <c r="B38" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>189</v>
@@ -10864,7 +10867,7 @@
     </row>
     <row r="39" spans="2:9" ht="13.15">
       <c r="B39" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>189</v>
@@ -10881,7 +10884,7 @@
     </row>
     <row r="40" spans="2:9" ht="13.15">
       <c r="B40" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>189</v>
@@ -10898,7 +10901,7 @@
     </row>
     <row r="41" spans="2:9" ht="13.15">
       <c r="B41" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>189</v>
@@ -10915,7 +10918,7 @@
     </row>
     <row r="42" spans="2:9" ht="13.15">
       <c r="B42" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>189</v>
@@ -10932,7 +10935,7 @@
     </row>
     <row r="43" spans="2:9" ht="13.15">
       <c r="B43" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>189</v>
@@ -10949,7 +10952,7 @@
     </row>
     <row r="44" spans="2:9" ht="13.15">
       <c r="B44" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>189</v>
@@ -10966,7 +10969,7 @@
     </row>
     <row r="45" spans="2:9" ht="13.15">
       <c r="B45" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>190</v>
@@ -10983,7 +10986,7 @@
     </row>
     <row r="46" spans="2:9" ht="13.15">
       <c r="B46" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>189</v>
@@ -11000,7 +11003,7 @@
     </row>
     <row r="47" spans="2:9" ht="13.15">
       <c r="B47" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>189</v>
@@ -11017,7 +11020,7 @@
     </row>
     <row r="48" spans="2:9" ht="13.15">
       <c r="B48" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>189</v>
@@ -11034,7 +11037,7 @@
     </row>
     <row r="49" spans="2:9" ht="13.15">
       <c r="B49" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>189</v>
@@ -11051,7 +11054,7 @@
     </row>
     <row r="50" spans="2:9" ht="13.15">
       <c r="B50" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>189</v>
@@ -11068,7 +11071,7 @@
     </row>
     <row r="51" spans="2:9" ht="13.15">
       <c r="B51" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F51" s="11" t="str">
         <f>F46</f>
@@ -11088,7 +11091,7 @@
     </row>
     <row r="52" spans="2:9" ht="13.15">
       <c r="B52" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>191</v>
@@ -11102,7 +11105,7 @@
     </row>
     <row r="53" spans="2:9" ht="13.15">
       <c r="B53" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>191</v>
@@ -11116,7 +11119,7 @@
     </row>
     <row r="54" spans="2:9" ht="13.15">
       <c r="B54" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>191</v>
@@ -11128,7 +11131,10 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="55" spans="2:9">
+    <row r="55" spans="2:9" ht="13.15">
+      <c r="B55" s="19" t="s">
+        <v>152</v>
+      </c>
       <c r="F55" s="11" t="s">
         <v>191</v>
       </c>
@@ -11632,6 +11638,35 @@
       </c>
       <c r="I102" s="22">
         <f>I84</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="5:10" ht="12.75">
+      <c r="F103" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="G103" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="I103" s="11">
+        <f>I48*0.65</f>
+        <v>0.62724999999999997</v>
+      </c>
+    </row>
+    <row r="104" spans="5:10" ht="14.25">
+      <c r="F104" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="G104"/>
+      <c r="H104" s="21" t="str">
+        <f>H103</f>
+        <v>MioNZDollar</v>
+      </c>
+      <c r="I104" s="22">
+        <f>I86</f>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6B2E8B-A7AE-4812-A565-A6F4D792DE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E833A6-03D9-428F-9EA4-F8FD372BBE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="G12" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>msy5_2046</v>
+        <v>msy16_2050</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>608</v>
@@ -6140,8 +6140,7 @@
         <v>2021</v>
       </c>
       <c r="G15" s="6">
-        <f>G14+3</f>
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="I15" s="6">
         <v>5</v>
@@ -6167,7 +6166,7 @@
       </c>
       <c r="G16" s="6">
         <f>G15+5</f>
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="I16" s="6">
         <v>5</v>
@@ -6192,8 +6191,8 @@
         <v>2031</v>
       </c>
       <c r="G17" s="6">
-        <f>G16+10</f>
-        <v>2036</v>
+        <f>G16+1</f>
+        <v>2026</v>
       </c>
       <c r="I17" s="6">
         <v>5</v>
@@ -6218,8 +6217,8 @@
         <v>2036</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" ref="G18" si="3">G17+10</f>
-        <v>2046</v>
+        <f t="shared" ref="G18:G27" si="3">G17+1</f>
+        <v>2027</v>
       </c>
       <c r="I18" s="6">
         <v>5</v>
@@ -6243,6 +6242,10 @@
         <f>F18+10</f>
         <v>2046</v>
       </c>
+      <c r="G19" s="6">
+        <f t="shared" si="3"/>
+        <v>2028</v>
+      </c>
       <c r="I19" s="6">
         <v>5</v>
       </c>
@@ -6261,6 +6264,10 @@
         <f t="shared" si="2"/>
         <v>2046</v>
       </c>
+      <c r="G20" s="6">
+        <f t="shared" si="3"/>
+        <v>2029</v>
+      </c>
       <c r="I20" s="6">
         <v>5</v>
       </c>
@@ -6275,6 +6282,10 @@
       <c r="D21" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="G21" s="6">
+        <f t="shared" si="3"/>
+        <v>2030</v>
+      </c>
       <c r="I21" s="6">
         <v>5</v>
       </c>
@@ -6289,6 +6300,10 @@
       <c r="D22" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="G22" s="6">
+        <f t="shared" si="3"/>
+        <v>2031</v>
+      </c>
       <c r="I22" s="6">
         <v>5</v>
       </c>
@@ -6303,6 +6318,10 @@
       <c r="D23" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="G23" s="6">
+        <f t="shared" si="3"/>
+        <v>2032</v>
+      </c>
       <c r="I23" s="6">
         <v>5</v>
       </c>
@@ -6313,6 +6332,10 @@
       </c>
       <c r="D24" s="6" t="s">
         <v>46</v>
+      </c>
+      <c r="G24" s="6">
+        <f t="shared" si="3"/>
+        <v>2033</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="14.25">
@@ -6320,29 +6343,46 @@
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="G25" s="6">
+        <f t="shared" si="3"/>
+        <v>2034</v>
+      </c>
     </row>
     <row r="26" spans="2:10" ht="14.25">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="G26" s="6">
+        <f t="shared" si="3"/>
+        <v>2035</v>
+      </c>
     </row>
     <row r="27" spans="2:10" ht="14.25">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="G27" s="6">
+        <v>2040</v>
+      </c>
     </row>
     <row r="28" spans="2:10" ht="14.25">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="G28" s="6">
+        <v>2045</v>
+      </c>
     </row>
     <row r="29" spans="2:10" ht="14.25">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>46</v>
+      </c>
+      <c r="G29" s="6">
+        <v>2050</v>
       </c>
     </row>
     <row r="30" spans="2:10" ht="14.25">

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E833A6-03D9-428F-9EA4-F8FD372BBE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64823A3E-6A60-4ED8-8717-5EE4EB546A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="619">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="G12" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>msy16_2050</v>
+        <v>msy20_2050</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>608</v>
@@ -6217,7 +6217,7 @@
         <v>2036</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" ref="G18:G27" si="3">G17+1</f>
+        <f t="shared" ref="G18:G26" si="3">G17+1</f>
         <v>2027</v>
       </c>
       <c r="I18" s="6">
@@ -6364,7 +6364,8 @@
         <v>46</v>
       </c>
       <c r="G27" s="6">
-        <v>2040</v>
+        <f>G26+2</f>
+        <v>2037</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="14.25">
@@ -6373,7 +6374,8 @@
         <v>46</v>
       </c>
       <c r="G28" s="6">
-        <v>2045</v>
+        <f>G27+2</f>
+        <v>2039</v>
       </c>
     </row>
     <row r="29" spans="2:10" ht="14.25">
@@ -6382,20 +6384,49 @@
         <v>46</v>
       </c>
       <c r="G29" s="6">
-        <v>2050</v>
+        <f>G28+2</f>
+        <v>2041</v>
       </c>
     </row>
     <row r="30" spans="2:10" ht="14.25">
       <c r="B30" s="9"/>
+      <c r="D30" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" s="6">
+        <f>G29+2</f>
+        <v>2043</v>
+      </c>
     </row>
     <row r="31" spans="2:10" ht="14.25">
       <c r="B31" s="9"/>
+      <c r="D31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="6">
+        <f>G30+2</f>
+        <v>2045</v>
+      </c>
     </row>
     <row r="32" spans="2:10" ht="14.25">
       <c r="B32" s="9"/>
-    </row>
-    <row r="33" spans="2:2" ht="14.25">
+      <c r="D32" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="6">
+        <f>G31+2</f>
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="14.25">
       <c r="B33" s="9"/>
+      <c r="D33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G33" s="6">
+        <f>G32+3</f>
+        <v>2050</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64823A3E-6A60-4ED8-8717-5EE4EB546A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9895AAF1-C351-4372-B3DF-B8E504A57E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="619">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -6015,7 +6015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
-  <dimension ref="B3:J33"/>
+  <dimension ref="B3:K41"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.1328125" style="6" customWidth="1"/>
@@ -6027,38 +6027,38 @@
     <col min="8" max="16384" width="11.3984375" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:11">
       <c r="B3" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:11">
       <c r="B4" s="6">
         <v>2018</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:11">
       <c r="B7" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:11">
       <c r="B8" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:11">
       <c r="B11" s="6" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="14.25">
+    <row r="12" spans="2:11" ht="14.25">
       <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
@@ -6077,28 +6077,32 @@
         <f t="shared" si="0"/>
         <v>msy20_2050</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="H12" s="8" t="str">
+        <f t="shared" ref="H12" si="1">"msy"&amp;COUNT(H14:H45)&amp;"_"&amp;MAX(H14:H45)</f>
+        <v>msy28_2050</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="14.25">
+    <row r="13" spans="2:11" ht="14.25">
       <c r="B13" s="9">
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="6">
-        <v>1</v>
-      </c>
       <c r="J13" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" ht="14.25">
+      <c r="K13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="14.25">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -6106,25 +6110,29 @@
         <v>46</v>
       </c>
       <c r="E14" s="6">
-        <f t="shared" ref="E14:G14" si="1">$B$4</f>
+        <f t="shared" ref="E14:H14" si="2">$B$4</f>
         <v>2018</v>
       </c>
       <c r="F14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2018</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2018</v>
       </c>
-      <c r="I14" s="6">
+      <c r="H14" s="6">
+        <f t="shared" si="2"/>
+        <v>2018</v>
+      </c>
+      <c r="J14" s="6">
         <v>2</v>
       </c>
-      <c r="J14" s="6">
+      <c r="K14" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="14.25">
+    <row r="15" spans="2:11" ht="14.25">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -6142,14 +6150,17 @@
       <c r="G15" s="6">
         <v>2020</v>
       </c>
-      <c r="I15" s="6">
-        <v>5</v>
+      <c r="H15" s="6">
+        <v>2020</v>
       </c>
       <c r="J15" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" ht="14.25">
+      <c r="K15" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="14.25">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -6168,14 +6179,18 @@
         <f>G15+5</f>
         <v>2025</v>
       </c>
-      <c r="I16" s="6">
-        <v>5</v>
+      <c r="H16" s="6">
+        <f>H15+5</f>
+        <v>2025</v>
       </c>
       <c r="J16" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" ht="14.25">
+      <c r="K16" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="14.25">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -6183,7 +6198,7 @@
         <v>46</v>
       </c>
       <c r="E17" s="6">
-        <f t="shared" ref="E17:E20" si="2">E16+5</f>
+        <f t="shared" ref="E17:E20" si="3">E16+5</f>
         <v>2031</v>
       </c>
       <c r="F17" s="6">
@@ -6194,14 +6209,18 @@
         <f>G16+1</f>
         <v>2026</v>
       </c>
-      <c r="I17" s="6">
-        <v>5</v>
+      <c r="H17" s="6">
+        <f>H16+1</f>
+        <v>2026</v>
       </c>
       <c r="J17" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" ht="14.25">
+      <c r="K17" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="14.25">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -6209,7 +6228,7 @@
         <v>46</v>
       </c>
       <c r="E18" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2036</v>
       </c>
       <c r="F18" s="6">
@@ -6217,17 +6236,21 @@
         <v>2036</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" ref="G18:G26" si="3">G17+1</f>
+        <f t="shared" ref="G18:H26" si="4">G17+1</f>
         <v>2027</v>
       </c>
-      <c r="I18" s="6">
-        <v>5</v>
+      <c r="H18" s="6">
+        <f t="shared" si="4"/>
+        <v>2027</v>
       </c>
       <c r="J18" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" ht="14.25">
+      <c r="K18" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="14.25">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -6235,7 +6258,7 @@
         <v>46</v>
       </c>
       <c r="E19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2041</v>
       </c>
       <c r="F19" s="6">
@@ -6243,17 +6266,21 @@
         <v>2046</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2028</v>
       </c>
-      <c r="I19" s="6">
-        <v>5</v>
+      <c r="H19" s="6">
+        <f t="shared" si="4"/>
+        <v>2028</v>
       </c>
       <c r="J19" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" ht="14.25">
+      <c r="K19" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="14.25">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -6261,21 +6288,25 @@
         <v>46</v>
       </c>
       <c r="E20" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2046</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2029</v>
       </c>
-      <c r="I20" s="6">
-        <v>5</v>
+      <c r="H20" s="6">
+        <f t="shared" si="4"/>
+        <v>2029</v>
       </c>
       <c r="J20" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="14.25">
+      <c r="K20" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="14.25">
       <c r="B21" s="9">
         <v>10</v>
       </c>
@@ -6283,17 +6314,21 @@
         <v>46</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2030</v>
       </c>
-      <c r="I21" s="6">
-        <v>5</v>
+      <c r="H21" s="6">
+        <f t="shared" si="4"/>
+        <v>2030</v>
       </c>
       <c r="J21" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" ht="14.25">
+      <c r="K21" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="14.25">
       <c r="B22" s="9">
         <v>10</v>
       </c>
@@ -6301,17 +6336,21 @@
         <v>46</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2031</v>
       </c>
-      <c r="I22" s="6">
-        <v>5</v>
+      <c r="H22" s="6">
+        <f t="shared" si="4"/>
+        <v>2031</v>
       </c>
       <c r="J22" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" ht="14.25">
+      <c r="K22" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="14.25">
       <c r="B23" s="9">
         <v>10</v>
       </c>
@@ -6319,14 +6358,18 @@
         <v>46</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2032</v>
       </c>
-      <c r="I23" s="6">
+      <c r="H23" s="6">
+        <f t="shared" si="4"/>
+        <v>2032</v>
+      </c>
+      <c r="J23" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="14.25">
+    <row r="24" spans="2:11" ht="14.25">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -6334,97 +6377,209 @@
         <v>46</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2033</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" ht="14.25">
+      <c r="H24" s="6">
+        <f t="shared" si="4"/>
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="14.25">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2034</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" ht="14.25">
+      <c r="H25" s="6">
+        <f t="shared" si="4"/>
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="14.25">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G26" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2035</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" ht="14.25">
+      <c r="H26" s="6">
+        <f t="shared" si="4"/>
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="14.25">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G27" s="6">
-        <f>G26+2</f>
+        <f t="shared" ref="G27:H32" si="5">G26+2</f>
         <v>2037</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" ht="14.25">
+      <c r="H27" s="6">
+        <f t="shared" ref="H27" si="6">H26+1</f>
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="14.25">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G28" s="6">
-        <f>G27+2</f>
+        <f t="shared" si="5"/>
         <v>2039</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" ht="14.25">
+      <c r="H28" s="6">
+        <f t="shared" ref="H28" si="7">H27+1</f>
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="14.25">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G29" s="6">
-        <f>G28+2</f>
+        <f t="shared" si="5"/>
         <v>2041</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" ht="14.25">
+      <c r="H29" s="6">
+        <f t="shared" ref="H29" si="8">H28+1</f>
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="14.25">
       <c r="B30" s="9"/>
       <c r="D30" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G30" s="6">
-        <f>G29+2</f>
+        <f t="shared" si="5"/>
         <v>2043</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" ht="14.25">
+      <c r="H30" s="6">
+        <f t="shared" ref="H30" si="9">H29+1</f>
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="14.25">
       <c r="B31" s="9"/>
       <c r="D31" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G31" s="6">
-        <f>G30+2</f>
+        <f t="shared" si="5"/>
         <v>2045</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" ht="14.25">
+      <c r="H31" s="6">
+        <f t="shared" ref="H31" si="10">H30+1</f>
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="14.25">
       <c r="B32" s="9"/>
       <c r="D32" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G32" s="6">
-        <f>G31+2</f>
+        <f t="shared" si="5"/>
         <v>2047</v>
       </c>
-    </row>
-    <row r="33" spans="2:7" ht="14.25">
+      <c r="H32" s="6">
+        <f t="shared" ref="H32" si="11">H31+1</f>
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="14.25">
       <c r="B33" s="9"/>
       <c r="D33" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G33" s="6">
         <f>G32+3</f>
+        <v>2050</v>
+      </c>
+      <c r="H33" s="6">
+        <f t="shared" ref="H33" si="12">H32+1</f>
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="D34" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="6">
+        <f t="shared" ref="H34" si="13">H33+1</f>
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="D35" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H35" s="6">
+        <f t="shared" ref="H35" si="14">H34+1</f>
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="D36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H36" s="6">
+        <f t="shared" ref="H36" si="15">H35+1</f>
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="D37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H37" s="6">
+        <f t="shared" ref="H37" si="16">H36+1</f>
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="D38" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H38" s="6">
+        <f t="shared" ref="H38" si="17">H37+1</f>
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="D39" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H39" s="6">
+        <f t="shared" ref="H39" si="18">H38+1</f>
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="D40" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H40" s="6">
+        <f t="shared" ref="H40" si="19">H39+1</f>
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="D41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H41" s="6">
+        <f t="shared" ref="H41" si="20">H40+1</f>
         <v>2050</v>
       </c>
     </row>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9895AAF1-C351-4372-B3DF-B8E504A57E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E48C51-8FA1-4FE9-9F8D-BB26F26A8EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="F12" s="8" t="str">
         <f t="shared" ref="F12:G12" si="0">"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
-        <v>msy6_2046</v>
+        <v>msy6_2030</v>
       </c>
       <c r="G12" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6144,8 +6144,7 @@
         <v>2021</v>
       </c>
       <c r="F15" s="6">
-        <f>F14+3</f>
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G15" s="6">
         <v>2020</v>
@@ -6172,8 +6171,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>F15+5</f>
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="G16" s="6">
         <f>G15+5</f>
@@ -6202,8 +6200,7 @@
         <v>2031</v>
       </c>
       <c r="F17" s="6">
-        <f>F16+5</f>
-        <v>2031</v>
+        <v>2025</v>
       </c>
       <c r="G17" s="6">
         <f>G16+1</f>
@@ -6232,8 +6229,7 @@
         <v>2036</v>
       </c>
       <c r="F18" s="6">
-        <f>F17+5</f>
-        <v>2036</v>
+        <v>2026</v>
       </c>
       <c r="G18" s="6">
         <f t="shared" ref="G18:H26" si="4">G17+1</f>
@@ -6262,8 +6258,7 @@
         <v>2041</v>
       </c>
       <c r="F19" s="6">
-        <f>F18+10</f>
-        <v>2046</v>
+        <v>2030</v>
       </c>
       <c r="G19" s="6">
         <f t="shared" si="4"/>
@@ -6419,7 +6414,7 @@
         <v>46</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" ref="G27:H32" si="5">G26+2</f>
+        <f t="shared" ref="G27:G32" si="5">G26+2</f>
         <v>2037</v>
       </c>
       <c r="H27" s="6">

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E48C51-8FA1-4FE9-9F8D-BB26F26A8EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30803A2C-946C-4D40-BB9F-ABDBFCE2AB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="F12" s="8" t="str">
         <f t="shared" ref="F12:G12" si="0">"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
-        <v>msy6_2030</v>
+        <v>msy13_2050</v>
       </c>
       <c r="G12" s="8" t="str">
         <f t="shared" si="0"/>
@@ -6171,7 +6171,8 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <v>2024</v>
+        <f>F15+5</f>
+        <v>2025</v>
       </c>
       <c r="G16" s="6">
         <f>G15+5</f>
@@ -6200,7 +6201,8 @@
         <v>2031</v>
       </c>
       <c r="F17" s="6">
-        <v>2025</v>
+        <f>F16+2</f>
+        <v>2027</v>
       </c>
       <c r="G17" s="6">
         <f>G16+1</f>
@@ -6229,7 +6231,8 @@
         <v>2036</v>
       </c>
       <c r="F18" s="6">
-        <v>2026</v>
+        <f>F17+3</f>
+        <v>2030</v>
       </c>
       <c r="G18" s="6">
         <f t="shared" ref="G18:H26" si="4">G17+1</f>
@@ -6258,7 +6261,8 @@
         <v>2041</v>
       </c>
       <c r="F19" s="6">
-        <v>2030</v>
+        <f>F18+2</f>
+        <v>2032</v>
       </c>
       <c r="G19" s="6">
         <f t="shared" si="4"/>
@@ -6286,6 +6290,10 @@
         <f t="shared" si="3"/>
         <v>2046</v>
       </c>
+      <c r="F20" s="6">
+        <f>F19+3</f>
+        <v>2035</v>
+      </c>
       <c r="G20" s="6">
         <f t="shared" si="4"/>
         <v>2029</v>
@@ -6308,6 +6316,10 @@
       <c r="D21" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="F21" s="6">
+        <f>F20+2</f>
+        <v>2037</v>
+      </c>
       <c r="G21" s="6">
         <f t="shared" si="4"/>
         <v>2030</v>
@@ -6330,6 +6342,10 @@
       <c r="D22" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="F22" s="6">
+        <f>F21+3</f>
+        <v>2040</v>
+      </c>
       <c r="G22" s="6">
         <f t="shared" si="4"/>
         <v>2031</v>
@@ -6352,6 +6368,10 @@
       <c r="D23" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="F23" s="6">
+        <f>F22+2</f>
+        <v>2042</v>
+      </c>
       <c r="G23" s="6">
         <f t="shared" si="4"/>
         <v>2032</v>
@@ -6370,6 +6390,10 @@
       </c>
       <c r="D24" s="6" t="s">
         <v>46</v>
+      </c>
+      <c r="F24" s="6">
+        <f>F23+3</f>
+        <v>2045</v>
       </c>
       <c r="G24" s="6">
         <f t="shared" si="4"/>
@@ -6385,6 +6409,10 @@
       <c r="D25" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="F25" s="6">
+        <f>F24+2</f>
+        <v>2047</v>
+      </c>
       <c r="G25" s="6">
         <f t="shared" si="4"/>
         <v>2034</v>
@@ -6399,6 +6427,10 @@
       <c r="D26" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="F26" s="6">
+        <f>F25+3</f>
+        <v>2050</v>
+      </c>
       <c r="G26" s="6">
         <f t="shared" si="4"/>
         <v>2035</v>
@@ -6414,7 +6446,7 @@
         <v>46</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" ref="G27:G32" si="5">G26+2</f>
+        <f t="shared" ref="F27:G32" si="5">G26+2</f>
         <v>2037</v>
       </c>
       <c r="H27" s="6">

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30803A2C-946C-4D40-BB9F-ABDBFCE2AB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3791EE-3222-4A96-B6FD-C2E2CB2B6A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6015,7 +6015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
-  <dimension ref="B3:K41"/>
+  <dimension ref="B3:L41"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.1328125" style="6" customWidth="1"/>
@@ -6024,41 +6024,43 @@
     <col min="4" max="4" width="14.1328125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.86328125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="10.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="6"/>
+    <col min="8" max="8" width="11.3984375" style="6"/>
+    <col min="9" max="9" width="9.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="11.3984375" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11">
+    <row r="3" spans="2:12">
       <c r="B3" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="2:12">
       <c r="B4" s="6">
         <v>2018</v>
       </c>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="2:12">
       <c r="B7" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="2:12">
       <c r="B8" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="2:12">
       <c r="B11" s="6" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="14.25">
+    <row r="12" spans="2:12" ht="14.25">
       <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
@@ -6078,31 +6080,35 @@
         <v>msy20_2050</v>
       </c>
       <c r="H12" s="8" t="str">
-        <f t="shared" ref="H12" si="1">"msy"&amp;COUNT(H14:H45)&amp;"_"&amp;MAX(H14:H45)</f>
+        <f t="shared" ref="H12:I12" si="1">"msy"&amp;COUNT(H14:H45)&amp;"_"&amp;MAX(H14:H45)</f>
         <v>msy28_2050</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="I12" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>msy7_2030</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="L12" s="6" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="14.25">
+    <row r="13" spans="2:12" ht="14.25">
       <c r="B13" s="9">
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="6">
-        <v>1</v>
-      </c>
       <c r="K13" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="2:11" ht="14.25">
+      <c r="L13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="14.25">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -6110,7 +6116,7 @@
         <v>46</v>
       </c>
       <c r="E14" s="6">
-        <f t="shared" ref="E14:H14" si="2">$B$4</f>
+        <f t="shared" ref="E14:I14" si="2">$B$4</f>
         <v>2018</v>
       </c>
       <c r="F14" s="6">
@@ -6125,14 +6131,18 @@
         <f t="shared" si="2"/>
         <v>2018</v>
       </c>
-      <c r="J14" s="6">
+      <c r="I14" s="6">
+        <f t="shared" si="2"/>
+        <v>2018</v>
+      </c>
+      <c r="K14" s="6">
         <v>2</v>
       </c>
-      <c r="K14" s="6">
+      <c r="L14" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="14.25">
+    <row r="15" spans="2:12" ht="14.25">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -6152,14 +6162,17 @@
       <c r="H15" s="6">
         <v>2020</v>
       </c>
-      <c r="J15" s="6">
-        <v>5</v>
+      <c r="I15" s="6">
+        <v>2020</v>
       </c>
       <c r="K15" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="2:11" ht="14.25">
+      <c r="L15" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="14.25">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -6182,14 +6195,17 @@
         <f>H15+5</f>
         <v>2025</v>
       </c>
-      <c r="J16" s="6">
-        <v>5</v>
+      <c r="I16" s="6">
+        <v>2022</v>
       </c>
       <c r="K16" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="2:11" ht="14.25">
+      <c r="L16" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="14.25">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -6212,14 +6228,17 @@
         <f>H16+1</f>
         <v>2026</v>
       </c>
-      <c r="J17" s="6">
-        <v>5</v>
+      <c r="I17" s="6">
+        <v>2024</v>
       </c>
       <c r="K17" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" ht="14.25">
+      <c r="L17" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="14.25">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -6242,14 +6261,18 @@
         <f t="shared" si="4"/>
         <v>2027</v>
       </c>
-      <c r="J18" s="6">
-        <v>5</v>
+      <c r="I18" s="6">
+        <f t="shared" ref="I18" si="5">I17+1</f>
+        <v>2025</v>
       </c>
       <c r="K18" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="2:11" ht="14.25">
+      <c r="L18" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="14.25">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -6272,14 +6295,18 @@
         <f t="shared" si="4"/>
         <v>2028</v>
       </c>
-      <c r="J19" s="6">
-        <v>5</v>
+      <c r="I19" s="6">
+        <f>I18+2</f>
+        <v>2027</v>
       </c>
       <c r="K19" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="2:11" ht="14.25">
+      <c r="L19" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="14.25">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -6302,14 +6329,18 @@
         <f t="shared" si="4"/>
         <v>2029</v>
       </c>
-      <c r="J20" s="6">
-        <v>5</v>
+      <c r="I20" s="6">
+        <f>I19+3</f>
+        <v>2030</v>
       </c>
       <c r="K20" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" ht="14.25">
+      <c r="L20" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="14.25">
       <c r="B21" s="9">
         <v>10</v>
       </c>
@@ -6328,14 +6359,14 @@
         <f t="shared" si="4"/>
         <v>2030</v>
       </c>
-      <c r="J21" s="6">
-        <v>5</v>
-      </c>
       <c r="K21" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="2:11" ht="14.25">
+      <c r="L21" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="14.25">
       <c r="B22" s="9">
         <v>10</v>
       </c>
@@ -6354,14 +6385,14 @@
         <f t="shared" si="4"/>
         <v>2031</v>
       </c>
-      <c r="J22" s="6">
-        <v>5</v>
-      </c>
       <c r="K22" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="2:11" ht="14.25">
+      <c r="L22" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="14.25">
       <c r="B23" s="9">
         <v>10</v>
       </c>
@@ -6380,11 +6411,11 @@
         <f t="shared" si="4"/>
         <v>2032</v>
       </c>
-      <c r="J23" s="6">
+      <c r="K23" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="14.25">
+    <row r="24" spans="2:12" ht="14.25">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -6404,7 +6435,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="14.25">
+    <row r="25" spans="2:12" ht="14.25">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>46</v>
@@ -6422,7 +6453,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="14.25">
+    <row r="26" spans="2:12" ht="14.25">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>46</v>
@@ -6440,87 +6471,87 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="14.25">
+    <row r="27" spans="2:12" ht="14.25">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" ref="F27:G32" si="5">G26+2</f>
+        <f t="shared" ref="G27:G32" si="6">G26+2</f>
         <v>2037</v>
       </c>
       <c r="H27" s="6">
-        <f t="shared" ref="H27" si="6">H26+1</f>
+        <f t="shared" ref="H27" si="7">H26+1</f>
         <v>2036</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="14.25">
+    <row r="28" spans="2:12" ht="14.25">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2039</v>
       </c>
       <c r="H28" s="6">
-        <f t="shared" ref="H28" si="7">H27+1</f>
+        <f t="shared" ref="H28" si="8">H27+1</f>
         <v>2037</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="14.25">
+    <row r="29" spans="2:12" ht="14.25">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G29" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2041</v>
       </c>
       <c r="H29" s="6">
-        <f t="shared" ref="H29" si="8">H28+1</f>
+        <f t="shared" ref="H29" si="9">H28+1</f>
         <v>2038</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="14.25">
+    <row r="30" spans="2:12" ht="14.25">
       <c r="B30" s="9"/>
       <c r="D30" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2043</v>
       </c>
       <c r="H30" s="6">
-        <f t="shared" ref="H30" si="9">H29+1</f>
+        <f t="shared" ref="H30" si="10">H29+1</f>
         <v>2039</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="14.25">
+    <row r="31" spans="2:12" ht="14.25">
       <c r="B31" s="9"/>
       <c r="D31" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2045</v>
       </c>
       <c r="H31" s="6">
-        <f t="shared" ref="H31" si="10">H30+1</f>
+        <f t="shared" ref="H31" si="11">H30+1</f>
         <v>2040</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="14.25">
+    <row r="32" spans="2:12" ht="14.25">
       <c r="B32" s="9"/>
       <c r="D32" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2047</v>
       </c>
       <c r="H32" s="6">
-        <f t="shared" ref="H32" si="11">H31+1</f>
+        <f t="shared" ref="H32" si="12">H31+1</f>
         <v>2041</v>
       </c>
     </row>
@@ -6534,7 +6565,7 @@
         <v>2050</v>
       </c>
       <c r="H33" s="6">
-        <f t="shared" ref="H33" si="12">H32+1</f>
+        <f t="shared" ref="H33" si="13">H32+1</f>
         <v>2042</v>
       </c>
     </row>
@@ -6543,7 +6574,7 @@
         <v>46</v>
       </c>
       <c r="H34" s="6">
-        <f t="shared" ref="H34" si="13">H33+1</f>
+        <f t="shared" ref="H34" si="14">H33+1</f>
         <v>2043</v>
       </c>
     </row>
@@ -6552,7 +6583,7 @@
         <v>46</v>
       </c>
       <c r="H35" s="6">
-        <f t="shared" ref="H35" si="14">H34+1</f>
+        <f t="shared" ref="H35" si="15">H34+1</f>
         <v>2044</v>
       </c>
     </row>
@@ -6561,7 +6592,7 @@
         <v>46</v>
       </c>
       <c r="H36" s="6">
-        <f t="shared" ref="H36" si="15">H35+1</f>
+        <f t="shared" ref="H36" si="16">H35+1</f>
         <v>2045</v>
       </c>
     </row>
@@ -6570,7 +6601,7 @@
         <v>46</v>
       </c>
       <c r="H37" s="6">
-        <f t="shared" ref="H37" si="16">H36+1</f>
+        <f t="shared" ref="H37" si="17">H36+1</f>
         <v>2046</v>
       </c>
     </row>
@@ -6579,7 +6610,7 @@
         <v>46</v>
       </c>
       <c r="H38" s="6">
-        <f t="shared" ref="H38" si="17">H37+1</f>
+        <f t="shared" ref="H38" si="18">H37+1</f>
         <v>2047</v>
       </c>
     </row>
@@ -6588,7 +6619,7 @@
         <v>46</v>
       </c>
       <c r="H39" s="6">
-        <f t="shared" ref="H39" si="18">H38+1</f>
+        <f t="shared" ref="H39" si="19">H38+1</f>
         <v>2048</v>
       </c>
     </row>
@@ -6597,7 +6628,7 @@
         <v>46</v>
       </c>
       <c r="H40" s="6">
-        <f t="shared" ref="H40" si="19">H39+1</f>
+        <f t="shared" ref="H40" si="20">H39+1</f>
         <v>2049</v>
       </c>
     </row>
@@ -6606,7 +6637,7 @@
         <v>46</v>
       </c>
       <c r="H41" s="6">
-        <f t="shared" ref="H41" si="20">H40+1</f>
+        <f t="shared" ref="H41" si="21">H40+1</f>
         <v>2050</v>
       </c>
     </row>
